--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -535,7 +535,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 13/09/2026</t>
+          <t>Report as at 14/09/2026</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 13/09/2026</t>
+          <t>Report as at 14/09/2026</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 13/09/2026</t>
+          <t>Report as at 14/09/2026</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 13/09/2026</t>
+          <t>Report as at 14/09/2026</t>
         </is>
       </c>
     </row>
@@ -4905,7 +4905,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 13/09/2026</t>
+          <t>Report as at 14/09/2026</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 13/09/2026</t>
+          <t>Report as at 14/09/2026</t>
         </is>
       </c>
     </row>
@@ -5811,7 +5811,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 13/09/2026</t>
+          <t>Report as at 14/09/2026</t>
         </is>
       </c>
     </row>
@@ -6181,7 +6181,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 13/09/2026</t>
+          <t>Report as at 14/09/2026</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 13/09/2026</t>
+          <t>Report as at 14/09/2026</t>
         </is>
       </c>
     </row>
@@ -7129,7 +7129,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 13/09/2026</t>
+          <t>Report as at 14/09/2026</t>
         </is>
       </c>
     </row>
@@ -7491,7 +7491,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 13/09/2026</t>
+          <t>Report as at 14/09/2026</t>
         </is>
       </c>
     </row>
@@ -10876,7 +10876,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 13/09/2026</t>
+          <t>Report as at 14/09/2026</t>
         </is>
       </c>
     </row>
@@ -11388,7 +11388,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 13/09/2026</t>
+          <t>Report as at 14/09/2026</t>
         </is>
       </c>
     </row>
@@ -12003,7 +12003,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 13/09/2026</t>
+          <t>Report as at 14/09/2026</t>
         </is>
       </c>
     </row>
@@ -15652,7 +15652,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 13/09/2026</t>
+          <t>Report as at 14/09/2026</t>
         </is>
       </c>
     </row>
@@ -16169,7 +16169,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 13/09/2026</t>
+          <t>Report as at 14/09/2026</t>
         </is>
       </c>
     </row>
@@ -16515,7 +16515,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 13/09/2026</t>
+          <t>Report as at 14/09/2026</t>
         </is>
       </c>
     </row>
@@ -20581,7 +20581,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 13/09/2026</t>
+          <t>Report as at 14/09/2026</t>
         </is>
       </c>
     </row>
@@ -21012,7 +21012,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 13/09/2026</t>
+          <t>Report as at 14/09/2026</t>
         </is>
       </c>
     </row>
@@ -21374,7 +21374,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 13/09/2026</t>
+          <t>Report as at 14/09/2026</t>
         </is>
       </c>
     </row>
@@ -22420,7 +22420,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 13/09/2026</t>
+          <t>Report as at 14/09/2026</t>
         </is>
       </c>
     </row>
@@ -22648,7 +22648,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 13/09/2026</t>
+          <t>Report as at 14/09/2026</t>
         </is>
       </c>
     </row>
@@ -23543,7 +23543,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 13/09/2026</t>
+          <t>Report as at 14/09/2026</t>
         </is>
       </c>
     </row>
@@ -24139,7 +24139,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 13/09/2026</t>
+          <t>Report as at 14/09/2026</t>
         </is>
       </c>
     </row>
@@ -24619,7 +24619,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 13/09/2026</t>
+          <t>Report as at 14/09/2026</t>
         </is>
       </c>
     </row>
@@ -27406,7 +27406,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 13/09/2026</t>
+          <t>Report as at 14/09/2026</t>
         </is>
       </c>
     </row>
@@ -28554,7 +28554,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 13/09/2026</t>
+          <t>Report as at 14/09/2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -535,7 +535,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 14/09/2026</t>
+          <t>Report as at 15/09/2026</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 14/09/2026</t>
+          <t>Report as at 15/09/2026</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 14/09/2026</t>
+          <t>Report as at 15/09/2026</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 14/09/2026</t>
+          <t>Report as at 15/09/2026</t>
         </is>
       </c>
     </row>
@@ -4905,7 +4905,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 14/09/2026</t>
+          <t>Report as at 15/09/2026</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 14/09/2026</t>
+          <t>Report as at 15/09/2026</t>
         </is>
       </c>
     </row>
@@ -5811,7 +5811,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 14/09/2026</t>
+          <t>Report as at 15/09/2026</t>
         </is>
       </c>
     </row>
@@ -6181,7 +6181,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 14/09/2026</t>
+          <t>Report as at 15/09/2026</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 14/09/2026</t>
+          <t>Report as at 15/09/2026</t>
         </is>
       </c>
     </row>
@@ -7129,7 +7129,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 14/09/2026</t>
+          <t>Report as at 15/09/2026</t>
         </is>
       </c>
     </row>
@@ -7491,7 +7491,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 14/09/2026</t>
+          <t>Report as at 15/09/2026</t>
         </is>
       </c>
     </row>
@@ -10876,7 +10876,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 14/09/2026</t>
+          <t>Report as at 15/09/2026</t>
         </is>
       </c>
     </row>
@@ -11388,7 +11388,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 14/09/2026</t>
+          <t>Report as at 15/09/2026</t>
         </is>
       </c>
     </row>
@@ -12003,7 +12003,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 14/09/2026</t>
+          <t>Report as at 15/09/2026</t>
         </is>
       </c>
     </row>
@@ -15652,7 +15652,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 14/09/2026</t>
+          <t>Report as at 15/09/2026</t>
         </is>
       </c>
     </row>
@@ -16169,7 +16169,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 14/09/2026</t>
+          <t>Report as at 15/09/2026</t>
         </is>
       </c>
     </row>
@@ -16515,7 +16515,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 14/09/2026</t>
+          <t>Report as at 15/09/2026</t>
         </is>
       </c>
     </row>
@@ -20581,7 +20581,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 14/09/2026</t>
+          <t>Report as at 15/09/2026</t>
         </is>
       </c>
     </row>
@@ -21012,7 +21012,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 14/09/2026</t>
+          <t>Report as at 15/09/2026</t>
         </is>
       </c>
     </row>
@@ -21374,7 +21374,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 14/09/2026</t>
+          <t>Report as at 15/09/2026</t>
         </is>
       </c>
     </row>
@@ -22420,7 +22420,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 14/09/2026</t>
+          <t>Report as at 15/09/2026</t>
         </is>
       </c>
     </row>
@@ -22648,7 +22648,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 14/09/2026</t>
+          <t>Report as at 15/09/2026</t>
         </is>
       </c>
     </row>
@@ -23543,7 +23543,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 14/09/2026</t>
+          <t>Report as at 15/09/2026</t>
         </is>
       </c>
     </row>
@@ -24139,7 +24139,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 14/09/2026</t>
+          <t>Report as at 15/09/2026</t>
         </is>
       </c>
     </row>
@@ -24619,7 +24619,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 14/09/2026</t>
+          <t>Report as at 15/09/2026</t>
         </is>
       </c>
     </row>
@@ -27406,7 +27406,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 14/09/2026</t>
+          <t>Report as at 15/09/2026</t>
         </is>
       </c>
     </row>
@@ -28554,7 +28554,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 14/09/2026</t>
+          <t>Report as at 15/09/2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -535,7 +535,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 15/09/2026</t>
+          <t>Report as at 16/09/2026</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 15/09/2026</t>
+          <t>Report as at 16/09/2026</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 15/09/2026</t>
+          <t>Report as at 16/09/2026</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 15/09/2026</t>
+          <t>Report as at 16/09/2026</t>
         </is>
       </c>
     </row>
@@ -4905,7 +4905,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 15/09/2026</t>
+          <t>Report as at 16/09/2026</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 15/09/2026</t>
+          <t>Report as at 16/09/2026</t>
         </is>
       </c>
     </row>
@@ -5811,7 +5811,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 15/09/2026</t>
+          <t>Report as at 16/09/2026</t>
         </is>
       </c>
     </row>
@@ -6181,7 +6181,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 15/09/2026</t>
+          <t>Report as at 16/09/2026</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 15/09/2026</t>
+          <t>Report as at 16/09/2026</t>
         </is>
       </c>
     </row>
@@ -7129,7 +7129,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 15/09/2026</t>
+          <t>Report as at 16/09/2026</t>
         </is>
       </c>
     </row>
@@ -7491,7 +7491,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 15/09/2026</t>
+          <t>Report as at 16/09/2026</t>
         </is>
       </c>
     </row>
@@ -10876,7 +10876,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 15/09/2026</t>
+          <t>Report as at 16/09/2026</t>
         </is>
       </c>
     </row>
@@ -11388,7 +11388,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 15/09/2026</t>
+          <t>Report as at 16/09/2026</t>
         </is>
       </c>
     </row>
@@ -12003,7 +12003,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 15/09/2026</t>
+          <t>Report as at 16/09/2026</t>
         </is>
       </c>
     </row>
@@ -15652,7 +15652,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 15/09/2026</t>
+          <t>Report as at 16/09/2026</t>
         </is>
       </c>
     </row>
@@ -16169,7 +16169,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 15/09/2026</t>
+          <t>Report as at 16/09/2026</t>
         </is>
       </c>
     </row>
@@ -16515,7 +16515,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 15/09/2026</t>
+          <t>Report as at 16/09/2026</t>
         </is>
       </c>
     </row>
@@ -20581,7 +20581,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 15/09/2026</t>
+          <t>Report as at 16/09/2026</t>
         </is>
       </c>
     </row>
@@ -21012,7 +21012,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 15/09/2026</t>
+          <t>Report as at 16/09/2026</t>
         </is>
       </c>
     </row>
@@ -21374,7 +21374,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 15/09/2026</t>
+          <t>Report as at 16/09/2026</t>
         </is>
       </c>
     </row>
@@ -22420,7 +22420,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 15/09/2026</t>
+          <t>Report as at 16/09/2026</t>
         </is>
       </c>
     </row>
@@ -22648,7 +22648,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 15/09/2026</t>
+          <t>Report as at 16/09/2026</t>
         </is>
       </c>
     </row>
@@ -23543,7 +23543,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 15/09/2026</t>
+          <t>Report as at 16/09/2026</t>
         </is>
       </c>
     </row>
@@ -24139,7 +24139,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 15/09/2026</t>
+          <t>Report as at 16/09/2026</t>
         </is>
       </c>
     </row>
@@ -24619,7 +24619,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 15/09/2026</t>
+          <t>Report as at 16/09/2026</t>
         </is>
       </c>
     </row>
@@ -27406,7 +27406,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 15/09/2026</t>
+          <t>Report as at 16/09/2026</t>
         </is>
       </c>
     </row>
@@ -28554,7 +28554,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 15/09/2026</t>
+          <t>Report as at 16/09/2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -535,7 +535,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 16/09/2026</t>
+          <t>Report as at 17/09/2026</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 16/09/2026</t>
+          <t>Report as at 17/09/2026</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 16/09/2026</t>
+          <t>Report as at 17/09/2026</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 16/09/2026</t>
+          <t>Report as at 17/09/2026</t>
         </is>
       </c>
     </row>
@@ -4905,7 +4905,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 16/09/2026</t>
+          <t>Report as at 17/09/2026</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 16/09/2026</t>
+          <t>Report as at 17/09/2026</t>
         </is>
       </c>
     </row>
@@ -5811,7 +5811,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 16/09/2026</t>
+          <t>Report as at 17/09/2026</t>
         </is>
       </c>
     </row>
@@ -6181,7 +6181,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 16/09/2026</t>
+          <t>Report as at 17/09/2026</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 16/09/2026</t>
+          <t>Report as at 17/09/2026</t>
         </is>
       </c>
     </row>
@@ -7129,7 +7129,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 16/09/2026</t>
+          <t>Report as at 17/09/2026</t>
         </is>
       </c>
     </row>
@@ -7491,7 +7491,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 16/09/2026</t>
+          <t>Report as at 17/09/2026</t>
         </is>
       </c>
     </row>
@@ -10876,7 +10876,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 16/09/2026</t>
+          <t>Report as at 17/09/2026</t>
         </is>
       </c>
     </row>
@@ -11388,7 +11388,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 16/09/2026</t>
+          <t>Report as at 17/09/2026</t>
         </is>
       </c>
     </row>
@@ -12003,7 +12003,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 16/09/2026</t>
+          <t>Report as at 17/09/2026</t>
         </is>
       </c>
     </row>
@@ -15652,7 +15652,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 16/09/2026</t>
+          <t>Report as at 17/09/2026</t>
         </is>
       </c>
     </row>
@@ -16169,7 +16169,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 16/09/2026</t>
+          <t>Report as at 17/09/2026</t>
         </is>
       </c>
     </row>
@@ -16515,7 +16515,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 16/09/2026</t>
+          <t>Report as at 17/09/2026</t>
         </is>
       </c>
     </row>
@@ -20581,7 +20581,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 16/09/2026</t>
+          <t>Report as at 17/09/2026</t>
         </is>
       </c>
     </row>
@@ -21012,7 +21012,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 16/09/2026</t>
+          <t>Report as at 17/09/2026</t>
         </is>
       </c>
     </row>
@@ -21374,7 +21374,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 16/09/2026</t>
+          <t>Report as at 17/09/2026</t>
         </is>
       </c>
     </row>
@@ -22420,7 +22420,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 16/09/2026</t>
+          <t>Report as at 17/09/2026</t>
         </is>
       </c>
     </row>
@@ -22648,7 +22648,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 16/09/2026</t>
+          <t>Report as at 17/09/2026</t>
         </is>
       </c>
     </row>
@@ -23543,7 +23543,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 16/09/2026</t>
+          <t>Report as at 17/09/2026</t>
         </is>
       </c>
     </row>
@@ -24139,7 +24139,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 16/09/2026</t>
+          <t>Report as at 17/09/2026</t>
         </is>
       </c>
     </row>
@@ -24619,7 +24619,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 16/09/2026</t>
+          <t>Report as at 17/09/2026</t>
         </is>
       </c>
     </row>
@@ -27406,7 +27406,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 16/09/2026</t>
+          <t>Report as at 17/09/2026</t>
         </is>
       </c>
     </row>
@@ -28554,7 +28554,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 16/09/2026</t>
+          <t>Report as at 17/09/2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -514,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:P20"/>
+  <dimension ref="A2:P26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1554,6 +1554,252 @@
         <v/>
       </c>
       <c r="P20" s="8" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Taman Armani Balok Permai</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>45800</v>
+      </c>
+      <c r="D21" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>11565-33</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>ARMANI IDAMAN SDN. BHD.</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="n"/>
+      <c r="H21" s="10" t="n"/>
+      <c r="I21" s="11" t="n"/>
+      <c r="J21" s="10" t="n"/>
+      <c r="K21" s="10" t="n"/>
+      <c r="L21" s="11" t="n"/>
+      <c r="M21" s="12" t="n"/>
+      <c r="N21" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="O21" s="13">
+        <f>N21/$D$21</f>
+        <v/>
+      </c>
+      <c r="P21" s="8" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Taman Armani Seberang Balok</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>45769</v>
+      </c>
+      <c r="D22" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>11565-39</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>ARMANI IDAMAN SDN. BHD.</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="n"/>
+      <c r="H22" s="10" t="n"/>
+      <c r="I22" s="11" t="n"/>
+      <c r="J22" s="10" t="n"/>
+      <c r="K22" s="10" t="n"/>
+      <c r="L22" s="11" t="n"/>
+      <c r="M22" s="12" t="n"/>
+      <c r="N22" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="O22" s="13">
+        <f>N22/$D$22</f>
+        <v/>
+      </c>
+      <c r="P22" s="8" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Taman Armani Balok Perdana</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>46195</v>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>11565-40</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>ARMANI IDAMAN SDN. BHD.</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="n"/>
+      <c r="H23" s="10" t="n"/>
+      <c r="I23" s="11" t="n"/>
+      <c r="J23" s="10" t="n"/>
+      <c r="K23" s="10" t="n"/>
+      <c r="L23" s="11" t="n"/>
+      <c r="M23" s="12" t="n"/>
+      <c r="N23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="13">
+        <f>N23/$D$23</f>
+        <v/>
+      </c>
+      <c r="P23" s="8" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Taman Armani Padang Indah</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>46195</v>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>11565-41</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>ARMANI IDAMAN SDN. BHD.</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="n"/>
+      <c r="H24" s="10" t="n"/>
+      <c r="I24" s="11" t="n"/>
+      <c r="J24" s="10" t="n"/>
+      <c r="K24" s="10" t="n"/>
+      <c r="L24" s="11" t="n"/>
+      <c r="M24" s="12" t="n"/>
+      <c r="N24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="13">
+        <f>N24/$D$24</f>
+        <v/>
+      </c>
+      <c r="P24" s="8" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Taman Armani Mentakab Indah</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>46204</v>
+      </c>
+      <c r="D25" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>11565-42</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>ARMANI IDAMAN SDN. BHD.</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="n"/>
+      <c r="H25" s="10" t="n"/>
+      <c r="I25" s="11" t="n"/>
+      <c r="J25" s="10" t="n"/>
+      <c r="K25" s="10" t="n"/>
+      <c r="L25" s="11" t="n"/>
+      <c r="M25" s="12" t="n"/>
+      <c r="N25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="13">
+        <f>N25/$D$25</f>
+        <v/>
+      </c>
+      <c r="P25" s="8" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Residensi Madani Mawar</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>46211</v>
+      </c>
+      <c r="D26" s="10" t="n">
+        <v>600</v>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>13975-7</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>GOLDEN ARMANI SDN. BHD.</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="n"/>
+      <c r="H26" s="10" t="n"/>
+      <c r="I26" s="11" t="n"/>
+      <c r="J26" s="10" t="n"/>
+      <c r="K26" s="10" t="n"/>
+      <c r="L26" s="11" t="n"/>
+      <c r="M26" s="12" t="n"/>
+      <c r="N26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="13">
+        <f>N26/$D$26</f>
+        <v/>
+      </c>
+      <c r="P26" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -6739,7 +6985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:P9"/>
+  <dimension ref="A2:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -7160,6 +7406,47 @@
           <t>Latest sales - Block A: 359 units, Block B: 334 units, Block C: 293 units</t>
         </is>
       </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Hill Residence</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>46027</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>19346-4</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>MALTON DEVELOPMENT SDN. BHD.</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="n"/>
+      <c r="H10" s="10" t="n"/>
+      <c r="I10" s="11" t="n"/>
+      <c r="J10" s="10" t="n"/>
+      <c r="K10" s="10" t="n"/>
+      <c r="L10" s="11" t="n"/>
+      <c r="M10" s="12" t="n"/>
+      <c r="N10" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" s="13">
+        <f>N10/$D$10</f>
+        <v/>
+      </c>
+      <c r="P10" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -20565,7 +20852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:P9"/>
+  <dimension ref="A2:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -20974,6 +21261,47 @@
           <t>Latest sales - Block A: 468 units, Block B: 465 units</t>
         </is>
       </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Skyawani Cassia Residences 1</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>46198</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>3600</v>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>31282-1</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>SKYWORLD CASSIA DEVELOPMENT SDN. BHD.</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="n"/>
+      <c r="H10" s="10" t="n"/>
+      <c r="I10" s="11" t="n"/>
+      <c r="J10" s="10" t="n"/>
+      <c r="K10" s="10" t="n"/>
+      <c r="L10" s="11" t="n"/>
+      <c r="M10" s="12" t="n"/>
+      <c r="N10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="13">
+        <f>N10/$D$10</f>
+        <v/>
+      </c>
+      <c r="P10" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -35075,7 +35403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:P26"/>
+  <dimension ref="A2:P28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -36474,6 +36802,92 @@
       </c>
       <c r="P26" s="8" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Keeperz Suites</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>46097</v>
+      </c>
+      <c r="D27" s="10" t="n">
+        <v>493</v>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>31088-2</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>EXSIM WATERFRONT SDN. BHD.</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="n"/>
+      <c r="H27" s="10" t="n"/>
+      <c r="I27" s="11" t="n"/>
+      <c r="J27" s="10" t="n"/>
+      <c r="K27" s="10" t="n"/>
+      <c r="L27" s="11" t="n"/>
+      <c r="M27" s="12" t="n"/>
+      <c r="N27" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="O27" s="13">
+        <f>N27/$D$27</f>
+        <v/>
+      </c>
+      <c r="P27" s="8" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 1 units, Block B: 8 units</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Erinaz Suites @ Kubang Kerian</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="n">
+        <v>46239</v>
+      </c>
+      <c r="D28" s="10" t="n">
+        <v>361</v>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>30371-1</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>EXSIM KUBANG KERIAN SDN. BHD.</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="n"/>
+      <c r="H28" s="10" t="n"/>
+      <c r="I28" s="11" t="n"/>
+      <c r="J28" s="10" t="n"/>
+      <c r="K28" s="10" t="n"/>
+      <c r="L28" s="11" t="n"/>
+      <c r="M28" s="12" t="n"/>
+      <c r="N28" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="O28" s="13">
+        <f>N28/$D$28</f>
+        <v/>
+      </c>
+      <c r="P28" s="8" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="J3:L3"/>
@@ -36490,7 +36904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:M46"/>
+  <dimension ref="A2:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -38532,6 +38946,120 @@
       </c>
       <c r="M46" s="8" t="inlineStr"/>
     </row>
+    <row r="47">
+      <c r="A47" s="7" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>Taman Alma</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="n">
+        <v>45722</v>
+      </c>
+      <c r="D47" s="10" t="n">
+        <v>136</v>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>7777-11</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="inlineStr">
+        <is>
+          <t>KSL DEVELOPMENT SDN. BHD.</t>
+        </is>
+      </c>
+      <c r="G47" s="10" t="n"/>
+      <c r="H47" s="10" t="n"/>
+      <c r="I47" s="11" t="n"/>
+      <c r="J47" s="12" t="n"/>
+      <c r="K47" s="12" t="n">
+        <v>111</v>
+      </c>
+      <c r="L47" s="13">
+        <f>K47/$D$47</f>
+        <v/>
+      </c>
+      <c r="M47" s="8" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>Taman Alma</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="n">
+        <v>45722</v>
+      </c>
+      <c r="D48" s="10" t="n">
+        <v>193</v>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>7777-12</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>KSL DEVELOPMENT SDN. BHD.</t>
+        </is>
+      </c>
+      <c r="G48" s="10" t="n"/>
+      <c r="H48" s="10" t="n"/>
+      <c r="I48" s="11" t="n"/>
+      <c r="J48" s="12" t="n"/>
+      <c r="K48" s="12" t="n">
+        <v>166</v>
+      </c>
+      <c r="L48" s="13">
+        <f>K48/$D$48</f>
+        <v/>
+      </c>
+      <c r="M48" s="8" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>Taman Bestari Indah</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="n">
+        <v>45898</v>
+      </c>
+      <c r="D49" s="10" t="n">
+        <v>153</v>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>3390-76</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>KHOO SOON LEE REALTY SDN. BHD.</t>
+        </is>
+      </c>
+      <c r="G49" s="10" t="n"/>
+      <c r="H49" s="10" t="n"/>
+      <c r="I49" s="11" t="n"/>
+      <c r="J49" s="12" t="n"/>
+      <c r="K49" s="12" t="n">
+        <v>81</v>
+      </c>
+      <c r="L49" s="13">
+        <f>K49/$D$49</f>
+        <v/>
+      </c>
+      <c r="M49" s="8" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="J3:L3"/>

--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -538,7 +538,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 18/09/2026</t>
+          <t>Report as at 19/09/2026</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 18/09/2026</t>
+          <t>Report as at 19/09/2026</t>
         </is>
       </c>
     </row>
@@ -3827,7 +3827,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 18/09/2026</t>
+          <t>Report as at 19/09/2026</t>
         </is>
       </c>
     </row>
@@ -5149,7 +5149,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 18/09/2026</t>
+          <t>Report as at 19/09/2026</t>
         </is>
       </c>
     </row>
@@ -6348,7 +6348,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 18/09/2026</t>
+          <t>Report as at 19/09/2026</t>
         </is>
       </c>
     </row>
@@ -7009,7 +7009,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 18/09/2026</t>
+          <t>Report as at 19/09/2026</t>
         </is>
       </c>
     </row>
@@ -7488,7 +7488,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 18/09/2026</t>
+          <t>Report as at 19/09/2026</t>
         </is>
       </c>
     </row>
@@ -7935,7 +7935,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 18/09/2026</t>
+          <t>Report as at 19/09/2026</t>
         </is>
       </c>
     </row>
@@ -8626,7 +8626,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 18/09/2026</t>
+          <t>Report as at 19/09/2026</t>
         </is>
       </c>
     </row>
@@ -9117,7 +9117,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 18/09/2026</t>
+          <t>Report as at 19/09/2026</t>
         </is>
       </c>
     </row>
@@ -9560,7 +9560,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 18/09/2026</t>
+          <t>Report as at 19/09/2026</t>
         </is>
       </c>
     </row>
@@ -13990,7 +13990,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 18/09/2026</t>
+          <t>Report as at 19/09/2026</t>
         </is>
       </c>
     </row>
@@ -14607,7 +14607,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 18/09/2026</t>
+          <t>Report as at 19/09/2026</t>
         </is>
       </c>
     </row>
@@ -15398,7 +15398,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 18/09/2026</t>
+          <t>Report as at 19/09/2026</t>
         </is>
       </c>
     </row>
@@ -20216,7 +20216,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 18/09/2026</t>
+          <t>Report as at 19/09/2026</t>
         </is>
       </c>
     </row>
@@ -20876,7 +20876,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 18/09/2026</t>
+          <t>Report as at 19/09/2026</t>
         </is>
       </c>
     </row>
@@ -21340,7 +21340,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 18/09/2026</t>
+          <t>Report as at 19/09/2026</t>
         </is>
       </c>
     </row>
@@ -26726,7 +26726,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 18/09/2026</t>
+          <t>Report as at 19/09/2026</t>
         </is>
       </c>
     </row>
@@ -27230,7 +27230,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 18/09/2026</t>
+          <t>Report as at 19/09/2026</t>
         </is>
       </c>
     </row>
@@ -27664,7 +27664,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 18/09/2026</t>
+          <t>Report as at 19/09/2026</t>
         </is>
       </c>
     </row>
@@ -29018,7 +29018,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 18/09/2026</t>
+          <t>Report as at 19/09/2026</t>
         </is>
       </c>
     </row>
@@ -29285,7 +29285,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 18/09/2026</t>
+          <t>Report as at 19/09/2026</t>
         </is>
       </c>
     </row>
@@ -30436,7 +30436,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 18/09/2026</t>
+          <t>Report as at 19/09/2026</t>
         </is>
       </c>
     </row>
@@ -31164,7 +31164,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 18/09/2026</t>
+          <t>Report as at 19/09/2026</t>
         </is>
       </c>
     </row>
@@ -31771,7 +31771,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 18/09/2026</t>
+          <t>Report as at 19/09/2026</t>
         </is>
       </c>
     </row>
@@ -35427,7 +35427,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 18/09/2026</t>
+          <t>Report as at 19/09/2026</t>
         </is>
       </c>
     </row>
@@ -36925,7 +36925,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 18/09/2026</t>
+          <t>Report as at 19/09/2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -538,7 +538,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 19/09/2026</t>
+          <t>Report as at 20/09/2026</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 19/09/2026</t>
+          <t>Report as at 20/09/2026</t>
         </is>
       </c>
     </row>
@@ -3827,7 +3827,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 19/09/2026</t>
+          <t>Report as at 20/09/2026</t>
         </is>
       </c>
     </row>
@@ -5149,7 +5149,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 19/09/2026</t>
+          <t>Report as at 20/09/2026</t>
         </is>
       </c>
     </row>
@@ -6348,7 +6348,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 19/09/2026</t>
+          <t>Report as at 20/09/2026</t>
         </is>
       </c>
     </row>
@@ -7009,7 +7009,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 19/09/2026</t>
+          <t>Report as at 20/09/2026</t>
         </is>
       </c>
     </row>
@@ -7488,7 +7488,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 19/09/2026</t>
+          <t>Report as at 20/09/2026</t>
         </is>
       </c>
     </row>
@@ -7935,7 +7935,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 19/09/2026</t>
+          <t>Report as at 20/09/2026</t>
         </is>
       </c>
     </row>
@@ -8626,7 +8626,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 19/09/2026</t>
+          <t>Report as at 20/09/2026</t>
         </is>
       </c>
     </row>
@@ -9117,7 +9117,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 19/09/2026</t>
+          <t>Report as at 20/09/2026</t>
         </is>
       </c>
     </row>
@@ -9560,7 +9560,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 19/09/2026</t>
+          <t>Report as at 20/09/2026</t>
         </is>
       </c>
     </row>
@@ -13990,7 +13990,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 19/09/2026</t>
+          <t>Report as at 20/09/2026</t>
         </is>
       </c>
     </row>
@@ -14607,7 +14607,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 19/09/2026</t>
+          <t>Report as at 20/09/2026</t>
         </is>
       </c>
     </row>
@@ -15398,7 +15398,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 19/09/2026</t>
+          <t>Report as at 20/09/2026</t>
         </is>
       </c>
     </row>
@@ -20216,7 +20216,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 19/09/2026</t>
+          <t>Report as at 20/09/2026</t>
         </is>
       </c>
     </row>
@@ -20876,7 +20876,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 19/09/2026</t>
+          <t>Report as at 20/09/2026</t>
         </is>
       </c>
     </row>
@@ -21340,7 +21340,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 19/09/2026</t>
+          <t>Report as at 20/09/2026</t>
         </is>
       </c>
     </row>
@@ -26726,7 +26726,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 19/09/2026</t>
+          <t>Report as at 20/09/2026</t>
         </is>
       </c>
     </row>
@@ -27230,7 +27230,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 19/09/2026</t>
+          <t>Report as at 20/09/2026</t>
         </is>
       </c>
     </row>
@@ -27664,7 +27664,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 19/09/2026</t>
+          <t>Report as at 20/09/2026</t>
         </is>
       </c>
     </row>
@@ -29018,7 +29018,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 19/09/2026</t>
+          <t>Report as at 20/09/2026</t>
         </is>
       </c>
     </row>
@@ -29285,7 +29285,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 19/09/2026</t>
+          <t>Report as at 20/09/2026</t>
         </is>
       </c>
     </row>
@@ -30436,7 +30436,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 19/09/2026</t>
+          <t>Report as at 20/09/2026</t>
         </is>
       </c>
     </row>
@@ -31164,7 +31164,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 19/09/2026</t>
+          <t>Report as at 20/09/2026</t>
         </is>
       </c>
     </row>
@@ -31771,7 +31771,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 19/09/2026</t>
+          <t>Report as at 20/09/2026</t>
         </is>
       </c>
     </row>
@@ -35427,7 +35427,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 19/09/2026</t>
+          <t>Report as at 20/09/2026</t>
         </is>
       </c>
     </row>
@@ -36925,7 +36925,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 19/09/2026</t>
+          <t>Report as at 20/09/2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -538,7 +538,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 20/09/2026</t>
+          <t>Report as at 21/09/2026</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 20/09/2026</t>
+          <t>Report as at 21/09/2026</t>
         </is>
       </c>
     </row>
@@ -3827,7 +3827,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 20/09/2026</t>
+          <t>Report as at 21/09/2026</t>
         </is>
       </c>
     </row>
@@ -5149,7 +5149,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 20/09/2026</t>
+          <t>Report as at 21/09/2026</t>
         </is>
       </c>
     </row>
@@ -6348,7 +6348,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 20/09/2026</t>
+          <t>Report as at 21/09/2026</t>
         </is>
       </c>
     </row>
@@ -7009,7 +7009,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 20/09/2026</t>
+          <t>Report as at 21/09/2026</t>
         </is>
       </c>
     </row>
@@ -7488,7 +7488,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 20/09/2026</t>
+          <t>Report as at 21/09/2026</t>
         </is>
       </c>
     </row>
@@ -7935,7 +7935,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 20/09/2026</t>
+          <t>Report as at 21/09/2026</t>
         </is>
       </c>
     </row>
@@ -8626,7 +8626,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 20/09/2026</t>
+          <t>Report as at 21/09/2026</t>
         </is>
       </c>
     </row>
@@ -9117,7 +9117,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 20/09/2026</t>
+          <t>Report as at 21/09/2026</t>
         </is>
       </c>
     </row>
@@ -9560,7 +9560,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 20/09/2026</t>
+          <t>Report as at 21/09/2026</t>
         </is>
       </c>
     </row>
@@ -13990,7 +13990,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 20/09/2026</t>
+          <t>Report as at 21/09/2026</t>
         </is>
       </c>
     </row>
@@ -14607,7 +14607,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 20/09/2026</t>
+          <t>Report as at 21/09/2026</t>
         </is>
       </c>
     </row>
@@ -15398,7 +15398,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 20/09/2026</t>
+          <t>Report as at 21/09/2026</t>
         </is>
       </c>
     </row>
@@ -20216,7 +20216,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 20/09/2026</t>
+          <t>Report as at 21/09/2026</t>
         </is>
       </c>
     </row>
@@ -20876,7 +20876,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 20/09/2026</t>
+          <t>Report as at 21/09/2026</t>
         </is>
       </c>
     </row>
@@ -21340,7 +21340,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 20/09/2026</t>
+          <t>Report as at 21/09/2026</t>
         </is>
       </c>
     </row>
@@ -26726,7 +26726,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 20/09/2026</t>
+          <t>Report as at 21/09/2026</t>
         </is>
       </c>
     </row>
@@ -27230,7 +27230,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 20/09/2026</t>
+          <t>Report as at 21/09/2026</t>
         </is>
       </c>
     </row>
@@ -27664,7 +27664,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 20/09/2026</t>
+          <t>Report as at 21/09/2026</t>
         </is>
       </c>
     </row>
@@ -29018,7 +29018,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 20/09/2026</t>
+          <t>Report as at 21/09/2026</t>
         </is>
       </c>
     </row>
@@ -29285,7 +29285,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 20/09/2026</t>
+          <t>Report as at 21/09/2026</t>
         </is>
       </c>
     </row>
@@ -30436,7 +30436,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 20/09/2026</t>
+          <t>Report as at 21/09/2026</t>
         </is>
       </c>
     </row>
@@ -31164,7 +31164,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 20/09/2026</t>
+          <t>Report as at 21/09/2026</t>
         </is>
       </c>
     </row>
@@ -31771,7 +31771,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 20/09/2026</t>
+          <t>Report as at 21/09/2026</t>
         </is>
       </c>
     </row>
@@ -35427,7 +35427,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 20/09/2026</t>
+          <t>Report as at 21/09/2026</t>
         </is>
       </c>
     </row>
@@ -36925,7 +36925,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 20/09/2026</t>
+          <t>Report as at 21/09/2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -514,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:P26"/>
+  <dimension ref="A2:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -538,7 +538,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 21/09/2026</t>
+          <t>Report as at 22/09/2026</t>
         </is>
       </c>
     </row>
@@ -934,28 +934,24 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Armani Residence Kepong</t>
+          <t>Armani Residence Setia Alam</t>
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>45436</v>
+        <v>45561</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>306</v>
+        <v>648</v>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>6820-8</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>MAGNA PARK SDN. BHD.</t>
-        </is>
-      </c>
+          <t>30727-1</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr"/>
       <c r="G10" s="10" t="n"/>
       <c r="H10" s="10" t="n">
-        <v>277</v>
+        <v>573</v>
       </c>
       <c r="I10" s="11">
         <f>H10/$D$10</f>
@@ -966,7 +962,7 @@
         <v/>
       </c>
       <c r="K10" s="10" t="n">
-        <v>277</v>
+        <v>574</v>
       </c>
       <c r="L10" s="11">
         <f>K10/$D$10</f>
@@ -977,13 +973,17 @@
         <v/>
       </c>
       <c r="N10" s="12" t="n">
-        <v>277</v>
+        <v>574</v>
       </c>
       <c r="O10" s="13">
         <f>N10/$D$10</f>
         <v/>
       </c>
-      <c r="P10" s="8" t="inlineStr"/>
+      <c r="P10" s="8" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 93 units, Block B: 481 units</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -991,24 +991,24 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Armani Residence Setia Alam</t>
+          <t>Armani Residence Setia Alam 2</t>
         </is>
       </c>
       <c r="C11" s="9" t="n">
-        <v>45561</v>
+        <v>46162</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>648</v>
+        <v>998</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>30727-1</t>
+          <t>30727-2</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr"/>
       <c r="G11" s="10" t="n"/>
       <c r="H11" s="10" t="n">
-        <v>573</v>
+        <v>284</v>
       </c>
       <c r="I11" s="11">
         <f>H11/$D$11</f>
@@ -1019,7 +1019,7 @@
         <v/>
       </c>
       <c r="K11" s="10" t="n">
-        <v>574</v>
+        <v>289</v>
       </c>
       <c r="L11" s="11">
         <f>K11/$D$11</f>
@@ -1030,7 +1030,7 @@
         <v/>
       </c>
       <c r="N11" s="12" t="n">
-        <v>574</v>
+        <v>296</v>
       </c>
       <c r="O11" s="13">
         <f>N11/$D$11</f>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="P11" s="8" t="inlineStr">
         <is>
-          <t>Latest sales - Block A: 93 units, Block B: 481 units</t>
+          <t>Latest sales - Block A: 71 units, Block B: 225 units</t>
         </is>
       </c>
     </row>
@@ -1048,24 +1048,28 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Armani Residence Setia Alam 2</t>
+          <t>Armani Residence Shah Alam</t>
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>46162</v>
+        <v>45303</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>998</v>
+        <v>338</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>30727-2</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr"/>
+          <t>30339-1</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>ARMANI ALLIANCE SDN. BHD.</t>
+        </is>
+      </c>
       <c r="G12" s="10" t="n"/>
       <c r="H12" s="10" t="n">
-        <v>284</v>
+        <v>331</v>
       </c>
       <c r="I12" s="11">
         <f>H12/$D$12</f>
@@ -1076,7 +1080,7 @@
         <v/>
       </c>
       <c r="K12" s="10" t="n">
-        <v>289</v>
+        <v>331</v>
       </c>
       <c r="L12" s="11">
         <f>K12/$D$12</f>
@@ -1087,17 +1091,13 @@
         <v/>
       </c>
       <c r="N12" s="12" t="n">
-        <v>296</v>
+        <v>331</v>
       </c>
       <c r="O12" s="13">
         <f>N12/$D$12</f>
         <v/>
       </c>
-      <c r="P12" s="8" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 71 units, Block B: 225 units</t>
-        </is>
-      </c>
+      <c r="P12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -1105,28 +1105,28 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Armani Residence Shah Alam</t>
+          <t>Armani Signature Residence</t>
         </is>
       </c>
       <c r="C13" s="9" t="n">
-        <v>45303</v>
+        <v>45252</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>338</v>
+        <v>315</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>30339-1</t>
+          <t>13975-5</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>ARMANI ALLIANCE SDN. BHD.</t>
+          <t>GOLDEN ARMANI SDN. BHD.</t>
         </is>
       </c>
       <c r="G13" s="10" t="n"/>
       <c r="H13" s="10" t="n">
-        <v>331</v>
+        <v>266</v>
       </c>
       <c r="I13" s="11">
         <f>H13/$D$13</f>
@@ -1137,7 +1137,7 @@
         <v/>
       </c>
       <c r="K13" s="10" t="n">
-        <v>331</v>
+        <v>268</v>
       </c>
       <c r="L13" s="11">
         <f>K13/$D$13</f>
@@ -1148,13 +1148,17 @@
         <v/>
       </c>
       <c r="N13" s="12" t="n">
-        <v>331</v>
+        <v>269</v>
       </c>
       <c r="O13" s="13">
         <f>N13/$D$13</f>
         <v/>
       </c>
-      <c r="P13" s="8" t="inlineStr"/>
+      <c r="P13" s="8" t="inlineStr">
+        <is>
+          <t>Latest sales - Block 1: 87 units, Block 2: 82 units, Block 3: 100 units</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -1162,28 +1166,28 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Armani Signature Residence</t>
+          <t>Lofthill Residence</t>
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>45252</v>
+        <v>45506</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>315</v>
+        <v>653</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>13975-5</t>
+          <t>30641-1</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>GOLDEN ARMANI SDN. BHD.</t>
+          <t>LOFTHILL DEVELOPMENT SDN. BHD.</t>
         </is>
       </c>
       <c r="G14" s="10" t="n"/>
       <c r="H14" s="10" t="n">
-        <v>266</v>
+        <v>647</v>
       </c>
       <c r="I14" s="11">
         <f>H14/$D$14</f>
@@ -1194,7 +1198,7 @@
         <v/>
       </c>
       <c r="K14" s="10" t="n">
-        <v>268</v>
+        <v>647</v>
       </c>
       <c r="L14" s="11">
         <f>K14/$D$14</f>
@@ -1205,17 +1209,13 @@
         <v/>
       </c>
       <c r="N14" s="12" t="n">
-        <v>269</v>
+        <v>647</v>
       </c>
       <c r="O14" s="13">
         <f>N14/$D$14</f>
         <v/>
       </c>
-      <c r="P14" s="8" t="inlineStr">
-        <is>
-          <t>Latest sales - Block 1: 87 units, Block 2: 82 units, Block 3: 100 units</t>
-        </is>
-      </c>
+      <c r="P14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -1223,28 +1223,28 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Lofthill Residence</t>
+          <t>Residensi Armani Kg Baru 1</t>
         </is>
       </c>
       <c r="C15" s="9" t="n">
-        <v>45506</v>
+        <v>45632</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>653</v>
+        <v>387</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>30641-1</t>
+          <t>13975-6</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>LOFTHILL DEVELOPMENT SDN. BHD.</t>
+          <t>GOLDEN ARMANI SDN. BHD.</t>
         </is>
       </c>
       <c r="G15" s="10" t="n"/>
       <c r="H15" s="10" t="n">
-        <v>647</v>
+        <v>384</v>
       </c>
       <c r="I15" s="11">
         <f>H15/$D$15</f>
@@ -1255,7 +1255,7 @@
         <v/>
       </c>
       <c r="K15" s="10" t="n">
-        <v>647</v>
+        <v>384</v>
       </c>
       <c r="L15" s="11">
         <f>K15/$D$15</f>
@@ -1266,7 +1266,7 @@
         <v/>
       </c>
       <c r="N15" s="12" t="n">
-        <v>647</v>
+        <v>384</v>
       </c>
       <c r="O15" s="13">
         <f>N15/$D$15</f>
@@ -1280,28 +1280,28 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Residensi Armani Kg Baru 1</t>
+          <t>Residensi Armani Putra</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>45632</v>
+        <v>46183</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>387</v>
+        <v>984</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>13975-6</t>
+          <t>30799-1</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>GOLDEN ARMANI SDN. BHD.</t>
+          <t>GOLDEN CHAIN DEVELOPMENT SDN. BHD.</t>
         </is>
       </c>
       <c r="G16" s="10" t="n"/>
       <c r="H16" s="10" t="n">
-        <v>384</v>
+        <v>29</v>
       </c>
       <c r="I16" s="11">
         <f>H16/$D$16</f>
@@ -1312,7 +1312,7 @@
         <v/>
       </c>
       <c r="K16" s="10" t="n">
-        <v>384</v>
+        <v>34</v>
       </c>
       <c r="L16" s="11">
         <f>K16/$D$16</f>
@@ -1323,13 +1323,17 @@
         <v/>
       </c>
       <c r="N16" s="12" t="n">
-        <v>384</v>
+        <v>39</v>
       </c>
       <c r="O16" s="13">
         <f>N16/$D$16</f>
         <v/>
       </c>
-      <c r="P16" s="8" t="inlineStr"/>
+      <c r="P16" s="8" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 15 units, Block B: 24 units</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -1337,28 +1341,28 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Residensi Armani Putra</t>
+          <t>Taman Bukit Tualang 2</t>
         </is>
       </c>
       <c r="C17" s="9" t="n">
-        <v>46183</v>
+        <v>46238</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>984</v>
+        <v>30</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>30799-1</t>
+          <t>30393-1</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>GOLDEN CHAIN DEVELOPMENT SDN. BHD.</t>
+          <t>GOLDEN ARMANI DEVELOPMENT SDN. BHD.</t>
         </is>
       </c>
       <c r="G17" s="10" t="n"/>
       <c r="H17" s="10" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="I17" s="11">
         <f>H17/$D$17</f>
@@ -1369,7 +1373,7 @@
         <v/>
       </c>
       <c r="K17" s="10" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="L17" s="11">
         <f>K17/$D$17</f>
@@ -1380,17 +1384,13 @@
         <v/>
       </c>
       <c r="N17" s="12" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="O17" s="13">
         <f>N17/$D$17</f>
         <v/>
       </c>
-      <c r="P17" s="8" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 15 units, Block B: 24 units</t>
-        </is>
-      </c>
+      <c r="P17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -1398,28 +1398,24 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Taman Bukit Tualang 2</t>
+          <t>Armani Prestige</t>
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>46238</v>
+        <v>45862</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>30</v>
+        <v>280</v>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>30393-1</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>GOLDEN ARMANI DEVELOPMENT SDN. BHD.</t>
-        </is>
-      </c>
+          <t>30135-2</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr"/>
       <c r="G18" s="10" t="n"/>
       <c r="H18" s="10" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="I18" s="11">
         <f>H18/$D$18</f>
@@ -1430,7 +1426,7 @@
         <v/>
       </c>
       <c r="K18" s="10" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="L18" s="11">
         <f>K18/$D$18</f>
@@ -1441,7 +1437,7 @@
         <v/>
       </c>
       <c r="N18" s="12" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="O18" s="13">
         <f>N18/$D$18</f>
@@ -1455,24 +1451,24 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Armani Prestige</t>
+          <t>Taman PMINT Tebing Tembah 2</t>
         </is>
       </c>
       <c r="C19" s="9" t="n">
-        <v>45862</v>
+        <v>45167</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>280</v>
+        <v>116</v>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>30135-2</t>
+          <t>13970-3</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr"/>
       <c r="G19" s="10" t="n"/>
       <c r="H19" s="10" t="n">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="I19" s="11">
         <f>H19/$D$19</f>
@@ -1483,7 +1479,7 @@
         <v/>
       </c>
       <c r="K19" s="10" t="n">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="L19" s="11">
         <f>K19/$D$19</f>
@@ -1494,7 +1490,7 @@
         <v/>
       </c>
       <c r="N19" s="12" t="n">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="O19" s="13">
         <f>N19/$D$19</f>
@@ -1508,298 +1504,40 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Taman PMINT Tebing Tembah 2</t>
+          <t>Residensi Madani Mawar</t>
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>45167</v>
+        <v>46211</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>116</v>
+        <v>600</v>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>13970-3</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr"/>
+          <t>13975-7</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>GOLDEN ARMANI SDN. BHD.</t>
+        </is>
+      </c>
       <c r="G20" s="10" t="n"/>
-      <c r="H20" s="10" t="n">
-        <v>81</v>
-      </c>
-      <c r="I20" s="11">
-        <f>H20/$D$20</f>
-        <v/>
-      </c>
-      <c r="J20" s="10">
-        <f>K20-H20</f>
-        <v/>
-      </c>
-      <c r="K20" s="10" t="n">
-        <v>82</v>
-      </c>
-      <c r="L20" s="11">
-        <f>K20/$D$20</f>
-        <v/>
-      </c>
-      <c r="M20" s="12">
-        <f>N20-K20</f>
-        <v/>
-      </c>
+      <c r="H20" s="10" t="n"/>
+      <c r="I20" s="11" t="n"/>
+      <c r="J20" s="10" t="n"/>
+      <c r="K20" s="10" t="n"/>
+      <c r="L20" s="11" t="n"/>
+      <c r="M20" s="12" t="n"/>
       <c r="N20" s="12" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="O20" s="13">
         <f>N20/$D$20</f>
         <v/>
       </c>
       <c r="P20" s="8" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>Taman Armani Balok Permai</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="n">
-        <v>45800</v>
-      </c>
-      <c r="D21" s="10" t="n">
-        <v>28</v>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>11565-33</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>ARMANI IDAMAN SDN. BHD.</t>
-        </is>
-      </c>
-      <c r="G21" s="10" t="n"/>
-      <c r="H21" s="10" t="n"/>
-      <c r="I21" s="11" t="n"/>
-      <c r="J21" s="10" t="n"/>
-      <c r="K21" s="10" t="n"/>
-      <c r="L21" s="11" t="n"/>
-      <c r="M21" s="12" t="n"/>
-      <c r="N21" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="O21" s="13">
-        <f>N21/$D$21</f>
-        <v/>
-      </c>
-      <c r="P21" s="8" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Taman Armani Seberang Balok</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="n">
-        <v>45769</v>
-      </c>
-      <c r="D22" s="10" t="n">
-        <v>29</v>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>11565-39</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>ARMANI IDAMAN SDN. BHD.</t>
-        </is>
-      </c>
-      <c r="G22" s="10" t="n"/>
-      <c r="H22" s="10" t="n"/>
-      <c r="I22" s="11" t="n"/>
-      <c r="J22" s="10" t="n"/>
-      <c r="K22" s="10" t="n"/>
-      <c r="L22" s="11" t="n"/>
-      <c r="M22" s="12" t="n"/>
-      <c r="N22" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="O22" s="13">
-        <f>N22/$D$22</f>
-        <v/>
-      </c>
-      <c r="P22" s="8" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>Taman Armani Balok Perdana</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="n">
-        <v>46195</v>
-      </c>
-      <c r="D23" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>11565-40</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>ARMANI IDAMAN SDN. BHD.</t>
-        </is>
-      </c>
-      <c r="G23" s="10" t="n"/>
-      <c r="H23" s="10" t="n"/>
-      <c r="I23" s="11" t="n"/>
-      <c r="J23" s="10" t="n"/>
-      <c r="K23" s="10" t="n"/>
-      <c r="L23" s="11" t="n"/>
-      <c r="M23" s="12" t="n"/>
-      <c r="N23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" s="13">
-        <f>N23/$D$23</f>
-        <v/>
-      </c>
-      <c r="P23" s="8" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Taman Armani Padang Indah</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="n">
-        <v>46195</v>
-      </c>
-      <c r="D24" s="10" t="n">
-        <v>28</v>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>11565-41</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>ARMANI IDAMAN SDN. BHD.</t>
-        </is>
-      </c>
-      <c r="G24" s="10" t="n"/>
-      <c r="H24" s="10" t="n"/>
-      <c r="I24" s="11" t="n"/>
-      <c r="J24" s="10" t="n"/>
-      <c r="K24" s="10" t="n"/>
-      <c r="L24" s="11" t="n"/>
-      <c r="M24" s="12" t="n"/>
-      <c r="N24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="13">
-        <f>N24/$D$24</f>
-        <v/>
-      </c>
-      <c r="P24" s="8" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Taman Armani Mentakab Indah</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="n">
-        <v>46204</v>
-      </c>
-      <c r="D25" s="10" t="n">
-        <v>28</v>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>11565-42</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>ARMANI IDAMAN SDN. BHD.</t>
-        </is>
-      </c>
-      <c r="G25" s="10" t="n"/>
-      <c r="H25" s="10" t="n"/>
-      <c r="I25" s="11" t="n"/>
-      <c r="J25" s="10" t="n"/>
-      <c r="K25" s="10" t="n"/>
-      <c r="L25" s="11" t="n"/>
-      <c r="M25" s="12" t="n"/>
-      <c r="N25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" s="13">
-        <f>N25/$D$25</f>
-        <v/>
-      </c>
-      <c r="P25" s="8" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>Residensi Madani Mawar</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="n">
-        <v>46211</v>
-      </c>
-      <c r="D26" s="10" t="n">
-        <v>600</v>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>13975-7</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>GOLDEN ARMANI SDN. BHD.</t>
-        </is>
-      </c>
-      <c r="G26" s="10" t="n"/>
-      <c r="H26" s="10" t="n"/>
-      <c r="I26" s="11" t="n"/>
-      <c r="J26" s="10" t="n"/>
-      <c r="K26" s="10" t="n"/>
-      <c r="L26" s="11" t="n"/>
-      <c r="M26" s="12" t="n"/>
-      <c r="N26" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="13">
-        <f>N26/$D$26</f>
-        <v/>
-      </c>
-      <c r="P26" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1817,7 +1555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:M45"/>
+  <dimension ref="A2:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1838,7 +1576,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 21/09/2026</t>
+          <t>Report as at 22/09/2026</t>
         </is>
       </c>
     </row>
@@ -2759,28 +2497,28 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Residensi Jati De Meru</t>
+          <t>Lagenda Suria (Phase 1A/1B)</t>
         </is>
       </c>
       <c r="C23" s="9" t="n">
-        <v>45302</v>
+        <v>45171</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>1084</v>
+        <v>608</v>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>30155-1</t>
+          <t>30223-1</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>MAJU TELUK BATIK SDN BHD.</t>
+          <t>LAGENDA MERSING  SDN. BHD.</t>
         </is>
       </c>
       <c r="G23" s="10" t="n"/>
       <c r="H23" s="10" t="n">
-        <v>911</v>
+        <v>606</v>
       </c>
       <c r="I23" s="11">
         <f>H23/$D$23</f>
@@ -2791,17 +2529,13 @@
         <v/>
       </c>
       <c r="K23" s="12" t="n">
-        <v>915</v>
+        <v>601</v>
       </c>
       <c r="L23" s="13">
         <f>K23/$D$23</f>
         <v/>
       </c>
-      <c r="M23" s="8" t="inlineStr">
-        <is>
-          <t>Latest sales - Block B: 436 units, Block C: 479 units</t>
-        </is>
-      </c>
+      <c r="M23" s="8" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -2809,28 +2543,28 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Residensi Jati De Meru (Phase 1B)</t>
+          <t>Lagenda Suria</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>46224</v>
+        <v>45398</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>1084</v>
+        <v>359</v>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>30155-2</t>
+          <t>30223-2</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>MAJU TELUK BATIK SDN BHD.</t>
+          <t>LAGENDA MERSING  SDN. BHD.</t>
         </is>
       </c>
       <c r="G24" s="10" t="n"/>
       <c r="H24" s="10" t="n">
-        <v>7</v>
+        <v>246</v>
       </c>
       <c r="I24" s="11">
         <f>H24/$D$24</f>
@@ -2841,17 +2575,13 @@
         <v/>
       </c>
       <c r="K24" s="12" t="n">
-        <v>9</v>
+        <v>249</v>
       </c>
       <c r="L24" s="13">
         <f>K24/$D$24</f>
         <v/>
       </c>
-      <c r="M24" s="8" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 9 units</t>
-        </is>
-      </c>
+      <c r="M24" s="8" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -2859,18 +2589,18 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Lagenda Suria (Phase 1A/1B)</t>
+          <t>La Lumiere (Nova/Lyra phases)</t>
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>45171</v>
+        <v>45744</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>608</v>
+        <v>893</v>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>30223-1</t>
+          <t>30223-3</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
@@ -2880,7 +2610,7 @@
       </c>
       <c r="G25" s="10" t="n"/>
       <c r="H25" s="10" t="n">
-        <v>606</v>
+        <v>748</v>
       </c>
       <c r="I25" s="11">
         <f>H25/$D$25</f>
@@ -2891,7 +2621,7 @@
         <v/>
       </c>
       <c r="K25" s="12" t="n">
-        <v>601</v>
+        <v>754</v>
       </c>
       <c r="L25" s="13">
         <f>K25/$D$25</f>
@@ -2905,18 +2635,18 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Lagenda Suria</t>
+          <t>La Lumiere</t>
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>45398</v>
+        <v>45862</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>359</v>
+        <v>1918</v>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>30223-2</t>
+          <t>30223-4</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
@@ -2926,7 +2656,7 @@
       </c>
       <c r="G26" s="10" t="n"/>
       <c r="H26" s="10" t="n">
-        <v>246</v>
+        <v>1721</v>
       </c>
       <c r="I26" s="11">
         <f>H26/$D$26</f>
@@ -2937,7 +2667,7 @@
         <v/>
       </c>
       <c r="K26" s="12" t="n">
-        <v>249</v>
+        <v>1737</v>
       </c>
       <c r="L26" s="13">
         <f>K26/$D$26</f>
@@ -2951,18 +2681,18 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>La Lumiere (Nova/Lyra phases)</t>
+          <t>Lagenda Suria - Samudra phase</t>
         </is>
       </c>
       <c r="C27" s="9" t="n">
-        <v>45744</v>
+        <v>45889</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>893</v>
+        <v>1379</v>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>30223-3</t>
+          <t>30223-5</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
@@ -2972,7 +2702,7 @@
       </c>
       <c r="G27" s="10" t="n"/>
       <c r="H27" s="10" t="n">
-        <v>748</v>
+        <v>369</v>
       </c>
       <c r="I27" s="11">
         <f>H27/$D$27</f>
@@ -2983,7 +2713,7 @@
         <v/>
       </c>
       <c r="K27" s="12" t="n">
-        <v>754</v>
+        <v>382</v>
       </c>
       <c r="L27" s="13">
         <f>K27/$D$27</f>
@@ -2997,18 +2727,18 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>La Lumiere</t>
+          <t>La Lumiere - Lexa phase</t>
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>45862</v>
+        <v>46094</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>1918</v>
+        <v>800</v>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>30223-4</t>
+          <t>30223-6</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
@@ -3018,7 +2748,7 @@
       </c>
       <c r="G28" s="10" t="n"/>
       <c r="H28" s="10" t="n">
-        <v>1721</v>
+        <v>460</v>
       </c>
       <c r="I28" s="11">
         <f>H28/$D$28</f>
@@ -3029,7 +2759,7 @@
         <v/>
       </c>
       <c r="K28" s="12" t="n">
-        <v>1737</v>
+        <v>472</v>
       </c>
       <c r="L28" s="13">
         <f>K28/$D$28</f>
@@ -3043,18 +2773,18 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Lagenda Suria - Samudra phase</t>
+          <t>La Lumiere - Rhea phase</t>
         </is>
       </c>
       <c r="C29" s="9" t="n">
-        <v>45889</v>
+        <v>46220</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1379</v>
+        <v>2013</v>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>30223-5</t>
+          <t>30223-7</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
@@ -3064,7 +2794,7 @@
       </c>
       <c r="G29" s="10" t="n"/>
       <c r="H29" s="10" t="n">
-        <v>369</v>
+        <v>3</v>
       </c>
       <c r="I29" s="11">
         <f>H29/$D$29</f>
@@ -3075,7 +2805,7 @@
         <v/>
       </c>
       <c r="K29" s="12" t="n">
-        <v>382</v>
+        <v>4</v>
       </c>
       <c r="L29" s="13">
         <f>K29/$D$29</f>
@@ -3089,28 +2819,28 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>La Lumiere - Lexa phase</t>
+          <t>Taman Pengkalan Impian (i-Molek)</t>
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>46094</v>
+        <v>45351</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>800</v>
+        <v>201</v>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>30223-6</t>
+          <t>30348-3</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>LAGENDA MERSING  SDN. BHD.</t>
+          <t>ANJURAN LAGENDA SDN. BHD.</t>
         </is>
       </c>
       <c r="G30" s="10" t="n"/>
       <c r="H30" s="10" t="n">
-        <v>460</v>
+        <v>200</v>
       </c>
       <c r="I30" s="11">
         <f>H30/$D$30</f>
@@ -3121,7 +2851,7 @@
         <v/>
       </c>
       <c r="K30" s="12" t="n">
-        <v>472</v>
+        <v>200</v>
       </c>
       <c r="L30" s="13">
         <f>K30/$D$30</f>
@@ -3135,28 +2865,28 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>La Lumiere - Rhea phase</t>
+          <t>Taman Pengkalan Impian</t>
         </is>
       </c>
       <c r="C31" s="9" t="n">
-        <v>46220</v>
+        <v>45824</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>2013</v>
+        <v>146</v>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>30223-7</t>
+          <t>30348-4</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>LAGENDA MERSING  SDN. BHD.</t>
+          <t>ANJURAN LAGENDA SDN. BHD.</t>
         </is>
       </c>
       <c r="G31" s="10" t="n"/>
       <c r="H31" s="10" t="n">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="I31" s="11">
         <f>H31/$D$31</f>
@@ -3167,7 +2897,7 @@
         <v/>
       </c>
       <c r="K31" s="12" t="n">
-        <v>4</v>
+        <v>79</v>
       </c>
       <c r="L31" s="13">
         <f>K31/$D$31</f>
@@ -3181,18 +2911,18 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Taman Pengkalan Impian (i-Molek)</t>
+          <t>Taman Pengkalan Impian</t>
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>45351</v>
+        <v>45910</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>30348-3</t>
+          <t>30348-5</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
@@ -3202,7 +2932,7 @@
       </c>
       <c r="G32" s="10" t="n"/>
       <c r="H32" s="10" t="n">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="I32" s="11">
         <f>H32/$D$32</f>
@@ -3213,7 +2943,7 @@
         <v/>
       </c>
       <c r="K32" s="12" t="n">
-        <v>200</v>
+        <v>174</v>
       </c>
       <c r="L32" s="13">
         <f>K32/$D$32</f>
@@ -3227,28 +2957,28 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Taman Pengkalan Impian</t>
+          <t>Lagenda Aman (Shorea/Dahlia phases)</t>
         </is>
       </c>
       <c r="C33" s="9" t="n">
-        <v>45824</v>
+        <v>45069</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>146</v>
+        <v>1449</v>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>30348-4</t>
+          <t>30377-1</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>ANJURAN LAGENDA SDN. BHD.</t>
+          <t>LAGENDA TAPAH  SDN. BHD.</t>
         </is>
       </c>
       <c r="G33" s="10" t="n"/>
       <c r="H33" s="10" t="n">
-        <v>78</v>
+        <v>1245</v>
       </c>
       <c r="I33" s="11">
         <f>H33/$D$33</f>
@@ -3259,7 +2989,7 @@
         <v/>
       </c>
       <c r="K33" s="12" t="n">
-        <v>79</v>
+        <v>1245</v>
       </c>
       <c r="L33" s="13">
         <f>K33/$D$33</f>
@@ -3273,28 +3003,24 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Taman Pengkalan Impian</t>
+          <t>Bidoria Residensi</t>
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>45910</v>
+        <v>45037</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>196</v>
+        <v>56</v>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>30348-5</t>
-        </is>
-      </c>
-      <c r="F34" s="8" t="inlineStr">
-        <is>
-          <t>ANJURAN LAGENDA SDN. BHD.</t>
-        </is>
-      </c>
+          <t>19950-2</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr"/>
       <c r="G34" s="10" t="n"/>
       <c r="H34" s="10" t="n">
-        <v>171</v>
+        <v>3</v>
       </c>
       <c r="I34" s="11">
         <f>H34/$D$34</f>
@@ -3305,7 +3031,7 @@
         <v/>
       </c>
       <c r="K34" s="12" t="n">
-        <v>174</v>
+        <v>3</v>
       </c>
       <c r="L34" s="13">
         <f>K34/$D$34</f>
@@ -3319,28 +3045,24 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>Lagenda Aman (Shorea/Dahlia phases)</t>
+          <t>Maxitanah Sdn. Bhd. Terraced Homes</t>
         </is>
       </c>
       <c r="C35" s="9" t="n">
-        <v>45069</v>
+        <v>44051</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>1449</v>
+        <v>397</v>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>30377-1</t>
-        </is>
-      </c>
-      <c r="F35" s="8" t="inlineStr">
-        <is>
-          <t>LAGENDA TAPAH  SDN. BHD.</t>
-        </is>
-      </c>
+          <t>19950-1</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr"/>
       <c r="G35" s="10" t="n"/>
       <c r="H35" s="10" t="n">
-        <v>1245</v>
+        <v>218</v>
       </c>
       <c r="I35" s="11">
         <f>H35/$D$35</f>
@@ -3351,7 +3073,7 @@
         <v/>
       </c>
       <c r="K35" s="12" t="n">
-        <v>1245</v>
+        <v>218</v>
       </c>
       <c r="L35" s="13">
         <f>K35/$D$35</f>
@@ -3365,28 +3087,24 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Taman Cinta Lagenda</t>
+          <t>Lagenda Teluk Intan</t>
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>45608</v>
+        <v>44533</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>124</v>
+        <v>1098</v>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>30781-1</t>
-        </is>
-      </c>
-      <c r="F36" s="8" t="inlineStr">
-        <is>
-          <t>LAGENDA ARMADA SDN. BHD.</t>
-        </is>
-      </c>
+          <t>14283-14</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr"/>
       <c r="G36" s="10" t="n"/>
       <c r="H36" s="10" t="n">
-        <v>0</v>
+        <v>781</v>
       </c>
       <c r="I36" s="11">
         <f>H36/$D$36</f>
@@ -3397,7 +3115,7 @@
         <v/>
       </c>
       <c r="K36" s="12" t="n">
-        <v>0</v>
+        <v>781</v>
       </c>
       <c r="L36" s="13">
         <f>K36/$D$36</f>
@@ -3411,28 +3129,24 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>Taman Kota Lagenda</t>
+          <t>Lagenda Tropika</t>
         </is>
       </c>
       <c r="C37" s="9" t="n">
-        <v>45352</v>
+        <v>44511</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>49</v>
+        <v>1783</v>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>7213-8</t>
-        </is>
-      </c>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>BERIBU LAGENDA SDN. BHD.</t>
-        </is>
-      </c>
+          <t>14283-13</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr"/>
       <c r="G37" s="10" t="n"/>
       <c r="H37" s="10" t="n">
-        <v>10</v>
+        <v>1435</v>
       </c>
       <c r="I37" s="11">
         <f>H37/$D$37</f>
@@ -3443,7 +3157,7 @@
         <v/>
       </c>
       <c r="K37" s="12" t="n">
-        <v>10</v>
+        <v>1435</v>
       </c>
       <c r="L37" s="13">
         <f>K37/$D$37</f>
@@ -3457,24 +3171,24 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>Bidoria Residensi</t>
+          <t>Bandar Baru Setiaawan Perdana</t>
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>45037</v>
+        <v>44545</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>56</v>
+        <v>668</v>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>19950-2</t>
+          <t>14283-15</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr"/>
       <c r="G38" s="10" t="n"/>
       <c r="H38" s="10" t="n">
-        <v>3</v>
+        <v>620</v>
       </c>
       <c r="I38" s="11">
         <f>H38/$D$38</f>
@@ -3485,7 +3199,7 @@
         <v/>
       </c>
       <c r="K38" s="12" t="n">
-        <v>3</v>
+        <v>620</v>
       </c>
       <c r="L38" s="13">
         <f>K38/$D$38</f>
@@ -3499,24 +3213,24 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>Maxitanah Sdn. Bhd. Terraced Homes</t>
+          <t>Taman Bemban Permai</t>
         </is>
       </c>
       <c r="C39" s="9" t="n">
-        <v>44051</v>
+        <v>43844</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>397</v>
+        <v>303</v>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>19950-1</t>
+          <t>14283-9</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr"/>
       <c r="G39" s="10" t="n"/>
       <c r="H39" s="10" t="n">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="I39" s="11">
         <f>H39/$D$39</f>
@@ -3527,7 +3241,7 @@
         <v/>
       </c>
       <c r="K39" s="12" t="n">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="L39" s="13">
         <f>K39/$D$39</f>
@@ -3541,24 +3255,24 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>Lagenda Teluk Intan</t>
+          <t>Taman Mulia Signature</t>
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>44533</v>
+        <v>43851</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>1098</v>
+        <v>242</v>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>14283-14</t>
+          <t>11225-9,11225-10</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr"/>
       <c r="G40" s="10" t="n"/>
       <c r="H40" s="10" t="n">
-        <v>781</v>
+        <v>119</v>
       </c>
       <c r="I40" s="11">
         <f>H40/$D$40</f>
@@ -3569,227 +3283,13 @@
         <v/>
       </c>
       <c r="K40" s="12" t="n">
-        <v>781</v>
+        <v>119</v>
       </c>
       <c r="L40" s="13">
         <f>K40/$D$40</f>
         <v/>
       </c>
       <c r="M40" s="8" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>Lagenda Tropika</t>
-        </is>
-      </c>
-      <c r="C41" s="9" t="n">
-        <v>44511</v>
-      </c>
-      <c r="D41" s="10" t="n">
-        <v>1783</v>
-      </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>14283-13</t>
-        </is>
-      </c>
-      <c r="F41" s="8" t="inlineStr"/>
-      <c r="G41" s="10" t="n"/>
-      <c r="H41" s="10" t="n">
-        <v>1435</v>
-      </c>
-      <c r="I41" s="11">
-        <f>H41/$D$41</f>
-        <v/>
-      </c>
-      <c r="J41" s="12">
-        <f>K41-H41</f>
-        <v/>
-      </c>
-      <c r="K41" s="12" t="n">
-        <v>1435</v>
-      </c>
-      <c r="L41" s="13">
-        <f>K41/$D$41</f>
-        <v/>
-      </c>
-      <c r="M41" s="8" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>Bandar Baru Setiaawan Perdana</t>
-        </is>
-      </c>
-      <c r="C42" s="9" t="n">
-        <v>44545</v>
-      </c>
-      <c r="D42" s="10" t="n">
-        <v>668</v>
-      </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>14283-15</t>
-        </is>
-      </c>
-      <c r="F42" s="8" t="inlineStr"/>
-      <c r="G42" s="10" t="n"/>
-      <c r="H42" s="10" t="n">
-        <v>620</v>
-      </c>
-      <c r="I42" s="11">
-        <f>H42/$D$42</f>
-        <v/>
-      </c>
-      <c r="J42" s="12">
-        <f>K42-H42</f>
-        <v/>
-      </c>
-      <c r="K42" s="12" t="n">
-        <v>620</v>
-      </c>
-      <c r="L42" s="13">
-        <f>K42/$D$42</f>
-        <v/>
-      </c>
-      <c r="M42" s="8" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="7" t="n">
-        <v>39</v>
-      </c>
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>Taman Bemban Permai</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="n">
-        <v>43844</v>
-      </c>
-      <c r="D43" s="10" t="n">
-        <v>303</v>
-      </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>14283-9</t>
-        </is>
-      </c>
-      <c r="F43" s="8" t="inlineStr"/>
-      <c r="G43" s="10" t="n"/>
-      <c r="H43" s="10" t="n">
-        <v>204</v>
-      </c>
-      <c r="I43" s="11">
-        <f>H43/$D$43</f>
-        <v/>
-      </c>
-      <c r="J43" s="12">
-        <f>K43-H43</f>
-        <v/>
-      </c>
-      <c r="K43" s="12" t="n">
-        <v>204</v>
-      </c>
-      <c r="L43" s="13">
-        <f>K43/$D$43</f>
-        <v/>
-      </c>
-      <c r="M43" s="8" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>Taman Mulia Signature</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="n">
-        <v>43851</v>
-      </c>
-      <c r="D44" s="10" t="n">
-        <v>242</v>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>11225-9,11225-10</t>
-        </is>
-      </c>
-      <c r="F44" s="8" t="inlineStr"/>
-      <c r="G44" s="10" t="n"/>
-      <c r="H44" s="10" t="n">
-        <v>119</v>
-      </c>
-      <c r="I44" s="11">
-        <f>H44/$D$44</f>
-        <v/>
-      </c>
-      <c r="J44" s="12">
-        <f>K44-H44</f>
-        <v/>
-      </c>
-      <c r="K44" s="12" t="n">
-        <v>119</v>
-      </c>
-      <c r="L44" s="13">
-        <f>K44/$D$44</f>
-        <v/>
-      </c>
-      <c r="M44" s="8" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="7" t="n">
-        <v>41</v>
-      </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>Taman Permai Jaya 2</t>
-        </is>
-      </c>
-      <c r="C45" s="9" t="n">
-        <v>46108</v>
-      </c>
-      <c r="D45" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>20128-2</t>
-        </is>
-      </c>
-      <c r="F45" s="8" t="inlineStr">
-        <is>
-          <t>HEKTAR MUDA SDN. BHD.</t>
-        </is>
-      </c>
-      <c r="G45" s="10" t="n"/>
-      <c r="H45" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="11">
-        <f>H45/$D$45</f>
-        <v/>
-      </c>
-      <c r="J45" s="12">
-        <f>K45-H45</f>
-        <v/>
-      </c>
-      <c r="K45" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" s="13">
-        <f>K45/$D$45</f>
-        <v/>
-      </c>
-      <c r="M45" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3827,7 +3327,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 21/09/2026</t>
+          <t>Report as at 22/09/2026</t>
         </is>
       </c>
     </row>
@@ -5149,7 +4649,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 21/09/2026</t>
+          <t>Report as at 22/09/2026</t>
         </is>
       </c>
     </row>
@@ -6348,7 +5848,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 21/09/2026</t>
+          <t>Report as at 22/09/2026</t>
         </is>
       </c>
     </row>
@@ -7009,7 +6509,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 21/09/2026</t>
+          <t>Report as at 22/09/2026</t>
         </is>
       </c>
     </row>
@@ -7488,7 +6988,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 21/09/2026</t>
+          <t>Report as at 22/09/2026</t>
         </is>
       </c>
     </row>
@@ -7935,7 +7435,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 21/09/2026</t>
+          <t>Report as at 22/09/2026</t>
         </is>
       </c>
     </row>
@@ -8626,7 +8126,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 21/09/2026</t>
+          <t>Report as at 22/09/2026</t>
         </is>
       </c>
     </row>
@@ -9117,7 +8617,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 21/09/2026</t>
+          <t>Report as at 22/09/2026</t>
         </is>
       </c>
     </row>
@@ -9560,7 +9060,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 21/09/2026</t>
+          <t>Report as at 22/09/2026</t>
         </is>
       </c>
     </row>
@@ -13990,7 +13490,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 21/09/2026</t>
+          <t>Report as at 22/09/2026</t>
         </is>
       </c>
     </row>
@@ -14586,7 +14086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:M18"/>
+  <dimension ref="A2:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -14607,7 +14107,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 21/09/2026</t>
+          <t>Report as at 22/09/2026</t>
         </is>
       </c>
     </row>
@@ -15359,6 +14859,80 @@
       <c r="M18" s="8" t="inlineStr">
         <is>
           <t>Latest sales - Block A: 289 units, Block B: 406 units, Block C: 135 units, Block D: 395 units, Block E: 396 units</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Residensi Jati De Meru</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>45302</v>
+      </c>
+      <c r="D19" s="10" t="n">
+        <v>1084</v>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>30155-1</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>MAJU TELUK BATIK SDN BHD.</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="n"/>
+      <c r="H19" s="10" t="n"/>
+      <c r="I19" s="11" t="n"/>
+      <c r="J19" s="12" t="n"/>
+      <c r="K19" s="12" t="n"/>
+      <c r="L19" s="13" t="n"/>
+      <c r="M19" s="8" t="inlineStr">
+        <is>
+          <t>Latest sales - Block B: 436 units, Block C: 479 units</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Residensi Jati De Meru (Phase 1B)</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>46224</v>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>1084</v>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>30155-2</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>MAJU TELUK BATIK SDN BHD.</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="n"/>
+      <c r="H20" s="10" t="n"/>
+      <c r="I20" s="11" t="n"/>
+      <c r="J20" s="12" t="n"/>
+      <c r="K20" s="12" t="n"/>
+      <c r="L20" s="13" t="n"/>
+      <c r="M20" s="8" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 9 units</t>
         </is>
       </c>
     </row>
@@ -15398,7 +14972,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 21/09/2026</t>
+          <t>Report as at 22/09/2026</t>
         </is>
       </c>
     </row>
@@ -20216,7 +19790,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 21/09/2026</t>
+          <t>Report as at 22/09/2026</t>
         </is>
       </c>
     </row>
@@ -20876,7 +20450,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 21/09/2026</t>
+          <t>Report as at 22/09/2026</t>
         </is>
       </c>
     </row>
@@ -21340,7 +20914,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 21/09/2026</t>
+          <t>Report as at 22/09/2026</t>
         </is>
       </c>
     </row>
@@ -26726,7 +26300,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 21/09/2026</t>
+          <t>Report as at 22/09/2026</t>
         </is>
       </c>
     </row>
@@ -27230,7 +26804,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 21/09/2026</t>
+          <t>Report as at 22/09/2026</t>
         </is>
       </c>
     </row>
@@ -27643,7 +27217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:M30"/>
+  <dimension ref="A2:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -27664,7 +27238,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 21/09/2026</t>
+          <t>Report as at 22/09/2026</t>
         </is>
       </c>
     </row>
@@ -28651,28 +28225,28 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Oskar Residence</t>
+          <t>KAIA Heights @ Equine Park</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>45322</v>
+        <v>44245</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>283</v>
+        <v>924</v>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>8024-13</t>
+          <t>20047-1,20047-2</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>SUNRISE MCL LAND SDN. BHD.</t>
+          <t>SUNRISE ALLIANCE SDN. BHD.</t>
         </is>
       </c>
       <c r="G24" s="10" t="n"/>
       <c r="H24" s="10" t="n">
-        <v>217</v>
+        <v>381</v>
       </c>
       <c r="I24" s="11">
         <f>H24/$D$24</f>
@@ -28683,13 +28257,17 @@
         <v/>
       </c>
       <c r="K24" s="12" t="n">
-        <v>217</v>
+        <v>381</v>
       </c>
       <c r="L24" s="13">
         <f>K24/$D$24</f>
         <v/>
       </c>
-      <c r="M24" s="8" t="inlineStr"/>
+      <c r="M24" s="8" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 112 units, Block B: 142 units, Block C: 59 units, Block D: 68 units</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -28697,28 +28275,28 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Arden Hill Precinct 2</t>
+          <t>Almãs Suites @ Iskandar Puteri</t>
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>45467</v>
+        <v>41633</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>218</v>
+        <v>546</v>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>8024-14</t>
+          <t>10555-12</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>SUNRISE MCL LAND SDN. BHD.</t>
+          <t>UEM LAND BERHAD</t>
         </is>
       </c>
       <c r="G25" s="10" t="n"/>
       <c r="H25" s="10" t="n">
-        <v>147</v>
+        <v>476</v>
       </c>
       <c r="I25" s="11">
         <f>H25/$D$25</f>
@@ -28729,13 +28307,17 @@
         <v/>
       </c>
       <c r="K25" s="12" t="n">
-        <v>148</v>
+        <v>476</v>
       </c>
       <c r="L25" s="13">
         <f>K25/$D$25</f>
         <v/>
       </c>
-      <c r="M25" s="8" t="inlineStr"/>
+      <c r="M25" s="8" t="inlineStr">
+        <is>
+          <t>Latest sales - Block C: 476 units</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -28743,28 +28325,28 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>KAIA Heights @ Equine Park</t>
+          <t>Intrika 1</t>
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>44245</v>
+        <v>45163</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>924</v>
+        <v>124</v>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>20047-1,20047-2</t>
+          <t>11186-16</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t>SUNRISE ALLIANCE SDN. BHD.</t>
+          <t>SYMPHONY HILLS SDN. BHD.</t>
         </is>
       </c>
       <c r="G26" s="10" t="n"/>
       <c r="H26" s="10" t="n">
-        <v>381</v>
+        <v>122</v>
       </c>
       <c r="I26" s="11">
         <f>H26/$D$26</f>
@@ -28775,17 +28357,13 @@
         <v/>
       </c>
       <c r="K26" s="12" t="n">
-        <v>381</v>
+        <v>122</v>
       </c>
       <c r="L26" s="13">
         <f>K26/$D$26</f>
         <v/>
       </c>
-      <c r="M26" s="8" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 112 units, Block B: 142 units, Block C: 59 units, Block D: 68 units</t>
-        </is>
-      </c>
+      <c r="M26" s="8" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -28793,28 +28371,28 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>Almãs Suites @ Iskandar Puteri</t>
+          <t>Intrika 2</t>
         </is>
       </c>
       <c r="C27" s="9" t="n">
-        <v>41633</v>
+        <v>45512</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>546</v>
+        <v>114</v>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>10555-12</t>
+          <t>11186-17</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>UEM LAND BERHAD</t>
+          <t>SYMPHONY HILLS SDN. BHD.</t>
         </is>
       </c>
       <c r="G27" s="10" t="n"/>
       <c r="H27" s="10" t="n">
-        <v>476</v>
+        <v>94</v>
       </c>
       <c r="I27" s="11">
         <f>H27/$D$27</f>
@@ -28825,159 +28403,13 @@
         <v/>
       </c>
       <c r="K27" s="12" t="n">
-        <v>476</v>
+        <v>94</v>
       </c>
       <c r="L27" s="13">
         <f>K27/$D$27</f>
         <v/>
       </c>
-      <c r="M27" s="8" t="inlineStr">
-        <is>
-          <t>Latest sales - Block C: 476 units</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>Radia Residences</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="n">
-        <v>41684</v>
-      </c>
-      <c r="D28" s="10" t="n">
-        <v>640</v>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>13373-1</t>
-        </is>
-      </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>SIME DARBY PROPERTY SUNRISE DEVELOPMENT SDN. BHD. (JV)</t>
-        </is>
-      </c>
-      <c r="G28" s="10" t="n"/>
-      <c r="H28" s="10" t="n">
-        <v>525</v>
-      </c>
-      <c r="I28" s="11">
-        <f>H28/$D$28</f>
-        <v/>
-      </c>
-      <c r="J28" s="12">
-        <f>K28-H28</f>
-        <v/>
-      </c>
-      <c r="K28" s="12" t="n">
-        <v>525</v>
-      </c>
-      <c r="L28" s="13">
-        <f>K28/$D$28</f>
-        <v/>
-      </c>
-      <c r="M28" s="8" t="inlineStr">
-        <is>
-          <t>Latest sales - Block B: 79 units, Block C: 141 units, Block D: 127 units, Block E: 131 units, Block F: 47 units</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>Intrika 1</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="n">
-        <v>45163</v>
-      </c>
-      <c r="D29" s="10" t="n">
-        <v>124</v>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>11186-16</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>SYMPHONY HILLS SDN. BHD.</t>
-        </is>
-      </c>
-      <c r="G29" s="10" t="n"/>
-      <c r="H29" s="10" t="n">
-        <v>122</v>
-      </c>
-      <c r="I29" s="11">
-        <f>H29/$D$29</f>
-        <v/>
-      </c>
-      <c r="J29" s="12">
-        <f>K29-H29</f>
-        <v/>
-      </c>
-      <c r="K29" s="12" t="n">
-        <v>122</v>
-      </c>
-      <c r="L29" s="13">
-        <f>K29/$D$29</f>
-        <v/>
-      </c>
-      <c r="M29" s="8" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>Intrika 2</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="n">
-        <v>45512</v>
-      </c>
-      <c r="D30" s="10" t="n">
-        <v>114</v>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>11186-17</t>
-        </is>
-      </c>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>SYMPHONY HILLS SDN. BHD.</t>
-        </is>
-      </c>
-      <c r="G30" s="10" t="n"/>
-      <c r="H30" s="10" t="n">
-        <v>94</v>
-      </c>
-      <c r="I30" s="11">
-        <f>H30/$D$30</f>
-        <v/>
-      </c>
-      <c r="J30" s="12">
-        <f>K30-H30</f>
-        <v/>
-      </c>
-      <c r="K30" s="12" t="n">
-        <v>94</v>
-      </c>
-      <c r="L30" s="13">
-        <f>K30/$D$30</f>
-        <v/>
-      </c>
-      <c r="M30" s="8" t="inlineStr"/>
+      <c r="M27" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -29018,7 +28450,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 21/09/2026</t>
+          <t>Report as at 22/09/2026</t>
         </is>
       </c>
     </row>
@@ -29285,7 +28717,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 21/09/2026</t>
+          <t>Report as at 22/09/2026</t>
         </is>
       </c>
     </row>
@@ -30436,7 +29868,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 21/09/2026</t>
+          <t>Report as at 22/09/2026</t>
         </is>
       </c>
     </row>
@@ -31164,7 +30596,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 21/09/2026</t>
+          <t>Report as at 22/09/2026</t>
         </is>
       </c>
     </row>
@@ -31771,7 +31203,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 21/09/2026</t>
+          <t>Report as at 22/09/2026</t>
         </is>
       </c>
     </row>
@@ -35427,7 +34859,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 21/09/2026</t>
+          <t>Report as at 22/09/2026</t>
         </is>
       </c>
     </row>
@@ -36925,7 +36357,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 21/09/2026</t>
+          <t>Report as at 22/09/2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -538,7 +538,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 22/09/2026</t>
+          <t>Report as at 23/09/2026</t>
         </is>
       </c>
     </row>
@@ -1576,7 +1576,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 22/09/2026</t>
+          <t>Report as at 23/09/2026</t>
         </is>
       </c>
     </row>
@@ -3327,7 +3327,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 22/09/2026</t>
+          <t>Report as at 23/09/2026</t>
         </is>
       </c>
     </row>
@@ -4649,7 +4649,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 22/09/2026</t>
+          <t>Report as at 23/09/2026</t>
         </is>
       </c>
     </row>
@@ -5848,7 +5848,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 22/09/2026</t>
+          <t>Report as at 23/09/2026</t>
         </is>
       </c>
     </row>
@@ -6509,7 +6509,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 22/09/2026</t>
+          <t>Report as at 23/09/2026</t>
         </is>
       </c>
     </row>
@@ -6988,7 +6988,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 22/09/2026</t>
+          <t>Report as at 23/09/2026</t>
         </is>
       </c>
     </row>
@@ -7435,7 +7435,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 22/09/2026</t>
+          <t>Report as at 23/09/2026</t>
         </is>
       </c>
     </row>
@@ -8126,7 +8126,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 22/09/2026</t>
+          <t>Report as at 23/09/2026</t>
         </is>
       </c>
     </row>
@@ -8617,7 +8617,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 22/09/2026</t>
+          <t>Report as at 23/09/2026</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 22/09/2026</t>
+          <t>Report as at 23/09/2026</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 22/09/2026</t>
+          <t>Report as at 23/09/2026</t>
         </is>
       </c>
     </row>
@@ -14107,7 +14107,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 22/09/2026</t>
+          <t>Report as at 23/09/2026</t>
         </is>
       </c>
     </row>
@@ -14972,7 +14972,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 22/09/2026</t>
+          <t>Report as at 23/09/2026</t>
         </is>
       </c>
     </row>
@@ -19790,7 +19790,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 22/09/2026</t>
+          <t>Report as at 23/09/2026</t>
         </is>
       </c>
     </row>
@@ -20450,7 +20450,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 22/09/2026</t>
+          <t>Report as at 23/09/2026</t>
         </is>
       </c>
     </row>
@@ -20914,7 +20914,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 22/09/2026</t>
+          <t>Report as at 23/09/2026</t>
         </is>
       </c>
     </row>
@@ -26300,7 +26300,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 22/09/2026</t>
+          <t>Report as at 23/09/2026</t>
         </is>
       </c>
     </row>
@@ -26804,7 +26804,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 22/09/2026</t>
+          <t>Report as at 23/09/2026</t>
         </is>
       </c>
     </row>
@@ -27238,7 +27238,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 22/09/2026</t>
+          <t>Report as at 23/09/2026</t>
         </is>
       </c>
     </row>
@@ -28450,7 +28450,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 22/09/2026</t>
+          <t>Report as at 23/09/2026</t>
         </is>
       </c>
     </row>
@@ -28717,7 +28717,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 22/09/2026</t>
+          <t>Report as at 23/09/2026</t>
         </is>
       </c>
     </row>
@@ -29868,7 +29868,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 22/09/2026</t>
+          <t>Report as at 23/09/2026</t>
         </is>
       </c>
     </row>
@@ -30596,7 +30596,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 22/09/2026</t>
+          <t>Report as at 23/09/2026</t>
         </is>
       </c>
     </row>
@@ -31203,7 +31203,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 22/09/2026</t>
+          <t>Report as at 23/09/2026</t>
         </is>
       </c>
     </row>
@@ -34859,7 +34859,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 22/09/2026</t>
+          <t>Report as at 23/09/2026</t>
         </is>
       </c>
     </row>
@@ -36357,7 +36357,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 22/09/2026</t>
+          <t>Report as at 23/09/2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -538,7 +538,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 23/09/2026</t>
+          <t>Report as at 24/09/2026</t>
         </is>
       </c>
     </row>
@@ -1576,7 +1576,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 23/09/2026</t>
+          <t>Report as at 24/09/2026</t>
         </is>
       </c>
     </row>
@@ -3327,7 +3327,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 23/09/2026</t>
+          <t>Report as at 24/09/2026</t>
         </is>
       </c>
     </row>
@@ -4649,7 +4649,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 23/09/2026</t>
+          <t>Report as at 24/09/2026</t>
         </is>
       </c>
     </row>
@@ -5848,7 +5848,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 23/09/2026</t>
+          <t>Report as at 24/09/2026</t>
         </is>
       </c>
     </row>
@@ -6509,7 +6509,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 23/09/2026</t>
+          <t>Report as at 24/09/2026</t>
         </is>
       </c>
     </row>
@@ -6988,7 +6988,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 23/09/2026</t>
+          <t>Report as at 24/09/2026</t>
         </is>
       </c>
     </row>
@@ -7435,7 +7435,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 23/09/2026</t>
+          <t>Report as at 24/09/2026</t>
         </is>
       </c>
     </row>
@@ -8126,7 +8126,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 23/09/2026</t>
+          <t>Report as at 24/09/2026</t>
         </is>
       </c>
     </row>
@@ -8617,7 +8617,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 23/09/2026</t>
+          <t>Report as at 24/09/2026</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 23/09/2026</t>
+          <t>Report as at 24/09/2026</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 23/09/2026</t>
+          <t>Report as at 24/09/2026</t>
         </is>
       </c>
     </row>
@@ -14107,7 +14107,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 23/09/2026</t>
+          <t>Report as at 24/09/2026</t>
         </is>
       </c>
     </row>
@@ -14972,7 +14972,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 23/09/2026</t>
+          <t>Report as at 24/09/2026</t>
         </is>
       </c>
     </row>
@@ -19790,7 +19790,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 23/09/2026</t>
+          <t>Report as at 24/09/2026</t>
         </is>
       </c>
     </row>
@@ -20450,7 +20450,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 23/09/2026</t>
+          <t>Report as at 24/09/2026</t>
         </is>
       </c>
     </row>
@@ -20914,7 +20914,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 23/09/2026</t>
+          <t>Report as at 24/09/2026</t>
         </is>
       </c>
     </row>
@@ -26300,7 +26300,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 23/09/2026</t>
+          <t>Report as at 24/09/2026</t>
         </is>
       </c>
     </row>
@@ -26804,7 +26804,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 23/09/2026</t>
+          <t>Report as at 24/09/2026</t>
         </is>
       </c>
     </row>
@@ -27238,7 +27238,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 23/09/2026</t>
+          <t>Report as at 24/09/2026</t>
         </is>
       </c>
     </row>
@@ -28450,7 +28450,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 23/09/2026</t>
+          <t>Report as at 24/09/2026</t>
         </is>
       </c>
     </row>
@@ -28717,7 +28717,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 23/09/2026</t>
+          <t>Report as at 24/09/2026</t>
         </is>
       </c>
     </row>
@@ -29868,7 +29868,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 23/09/2026</t>
+          <t>Report as at 24/09/2026</t>
         </is>
       </c>
     </row>
@@ -30596,7 +30596,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 23/09/2026</t>
+          <t>Report as at 24/09/2026</t>
         </is>
       </c>
     </row>
@@ -31203,7 +31203,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 23/09/2026</t>
+          <t>Report as at 24/09/2026</t>
         </is>
       </c>
     </row>
@@ -34859,7 +34859,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 23/09/2026</t>
+          <t>Report as at 24/09/2026</t>
         </is>
       </c>
     </row>
@@ -36357,7 +36357,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 23/09/2026</t>
+          <t>Report as at 24/09/2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -542,7 +542,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 24/09/2026</t>
+          <t>Report as at 25/09/2026</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 24/09/2026</t>
+          <t>Report as at 25/09/2026</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 24/09/2026</t>
+          <t>Report as at 25/09/2026</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 24/09/2026</t>
+          <t>Report as at 25/09/2026</t>
         </is>
       </c>
     </row>
@@ -6991,7 +6991,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 24/09/2026</t>
+          <t>Report as at 25/09/2026</t>
         </is>
       </c>
     </row>
@@ -7768,7 +7768,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 24/09/2026</t>
+          <t>Report as at 25/09/2026</t>
         </is>
       </c>
     </row>
@@ -8335,7 +8335,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 24/09/2026</t>
+          <t>Report as at 25/09/2026</t>
         </is>
       </c>
     </row>
@@ -8859,7 +8859,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 24/09/2026</t>
+          <t>Report as at 25/09/2026</t>
         </is>
       </c>
     </row>
@@ -9687,7 +9687,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 24/09/2026</t>
+          <t>Report as at 25/09/2026</t>
         </is>
       </c>
     </row>
@@ -9791,7 +9791,7 @@
       </c>
       <c r="J5" s="8" t="inlineStr">
         <is>
-          <t>TEDUH name PANGSAPURI PUTRA IDAMAN.</t>
+          <t>Latest sales - Block A: 225 units, Block B: 251 units</t>
         </is>
       </c>
     </row>
@@ -9830,7 +9830,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>Web lists 576 units; 384 (2 x 192) licensed so far.</t>
+          <t>Latest sales - Block B: 93 units</t>
         </is>
       </c>
     </row>
@@ -9867,11 +9867,7 @@
         <f>H7/$D$7</f>
         <v/>
       </c>
-      <c r="J7" s="8" t="inlineStr">
-        <is>
-          <t>Halaman 1 (30962-1, TEDUH name ALAM IMPIAN: 54 semi-D + 16 bungalow) + Halaman 2 (30962-2: 46 bungalow).</t>
-        </is>
-      </c>
+      <c r="J7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -9906,11 +9902,7 @@
         <f>H8/$D$8</f>
         <v/>
       </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>TEDUH name PANGSAPURI SAUJANA IDAMAN. Web lists 858 units; 286 licensed so far.</t>
-        </is>
-      </c>
+      <c r="J8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -10060,7 +10052,7 @@
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>TEDUH name RESIDENSI ALEA; 5534-29 (ALEA MYRA ALAM) is a superseded duplicate licence with no sales.</t>
+          <t>Latest sales - Block A: 66 units, Block B: 70 units, Block C: 78 units, Block D: 83 units</t>
         </is>
       </c>
     </row>
@@ -10099,7 +10091,7 @@
       </c>
       <c r="J13" s="8" t="inlineStr">
         <is>
-          <t>Ph1 (20164-1, 279 units) sold out.</t>
+          <t>Latest sales - Block B1: 159 units, Block B2: 7 units, Block B3: 29 units, Block B4: 20 units, Block B5: 23 units</t>
         </is>
       </c>
     </row>
@@ -10138,7 +10130,7 @@
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>TEDUH name MYRA IMPIAN. Web lists 546 units = this + Ara Residence (7935-8).</t>
+          <t>Latest sales - Block A: 235 units, Block B: 26 units</t>
         </is>
       </c>
     </row>
@@ -10177,7 +10169,7 @@
       </c>
       <c r="J15" s="8" t="inlineStr">
         <is>
-          <t>TEDUH name PANGSAPURI PERKHIDMATAN ARA NILAI IMPIAN.</t>
+          <t>Latest sales - Block B: 216 units</t>
         </is>
       </c>
     </row>
@@ -10214,11 +10206,7 @@
         <f>H16/$D$16</f>
         <v/>
       </c>
-      <c r="J16" s="8" t="inlineStr">
-        <is>
-          <t>Ph1-2 (20014-1, 20014-2) sold out.</t>
-        </is>
-      </c>
+      <c r="J16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -10255,7 +10243,7 @@
       </c>
       <c r="J17" s="8" t="inlineStr">
         <is>
-          <t>Not on myra.com.my yet (Sep 2026).</t>
+          <t>Latest sales - Block B: 63 units</t>
         </is>
       </c>
     </row>
@@ -10292,11 +10280,7 @@
         <f>H18/$D$18</f>
         <v/>
       </c>
-      <c r="J18" s="8" t="inlineStr">
-        <is>
-          <t>Earlier Myra Alam phases (5534-20, 21, 28) sold out.</t>
-        </is>
-      </c>
+      <c r="J18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -10331,11 +10315,7 @@
         <f>H19/$D$19</f>
         <v/>
       </c>
-      <c r="J19" s="8" t="inlineStr">
-        <is>
-          <t>TEDUH name PANGSAPURI IRINA.</t>
-        </is>
-      </c>
+      <c r="J19" s="8" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -10405,11 +10385,7 @@
         <f>H21/$D$21</f>
         <v/>
       </c>
-      <c r="J21" s="8" t="inlineStr">
-        <is>
-          <t>Ph1-2 (19355-1, 19355-2) sold out.</t>
-        </is>
-      </c>
+      <c r="J21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -10444,11 +10420,7 @@
         <f>H22/$D$22</f>
         <v/>
       </c>
-      <c r="J22" s="8" t="inlineStr">
-        <is>
-          <t>Not on myra.com.my yet (Sep 2026).</t>
-        </is>
-      </c>
+      <c r="J22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -10483,11 +10455,7 @@
         <f>H23/$D$23</f>
         <v/>
       </c>
-      <c r="J23" s="8" t="inlineStr">
-        <is>
-          <t>Not on myra.com.my yet (Sep 2026); 31 terrace units.</t>
-        </is>
-      </c>
+      <c r="J23" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -10530,7 +10498,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 24/09/2026</t>
+          <t>Report as at 25/09/2026</t>
         </is>
       </c>
     </row>
@@ -11109,7 +11077,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 24/09/2026</t>
+          <t>Report as at 25/09/2026</t>
         </is>
       </c>
     </row>
@@ -11632,7 +11600,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 24/09/2026</t>
+          <t>Report as at 25/09/2026</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12322,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 24/09/2026</t>
+          <t>Report as at 25/09/2026</t>
         </is>
       </c>
     </row>
@@ -17826,7 +17794,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 24/09/2026</t>
+          <t>Report as at 25/09/2026</t>
         </is>
       </c>
     </row>
@@ -18883,7 +18851,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 24/09/2026</t>
+          <t>Report as at 25/09/2026</t>
         </is>
       </c>
     </row>
@@ -24874,7 +24842,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 24/09/2026</t>
+          <t>Report as at 25/09/2026</t>
         </is>
       </c>
     </row>
@@ -25677,7 +25645,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 24/09/2026</t>
+          <t>Report as at 25/09/2026</t>
         </is>
       </c>
     </row>
@@ -26229,7 +26197,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 24/09/2026</t>
+          <t>Report as at 25/09/2026</t>
         </is>
       </c>
     </row>
@@ -32935,7 +32903,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 24/09/2026</t>
+          <t>Report as at 25/09/2026</t>
         </is>
       </c>
     </row>
@@ -33512,7 +33480,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 24/09/2026</t>
+          <t>Report as at 25/09/2026</t>
         </is>
       </c>
     </row>
@@ -34018,7 +33986,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 24/09/2026</t>
+          <t>Report as at 25/09/2026</t>
         </is>
       </c>
     </row>
@@ -35505,7 +35473,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 24/09/2026</t>
+          <t>Report as at 25/09/2026</t>
         </is>
       </c>
     </row>
@@ -35811,7 +35779,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 24/09/2026</t>
+          <t>Report as at 25/09/2026</t>
         </is>
       </c>
     </row>
@@ -37218,7 +37186,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 24/09/2026</t>
+          <t>Report as at 25/09/2026</t>
         </is>
       </c>
     </row>
@@ -38078,7 +38046,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 24/09/2026</t>
+          <t>Report as at 25/09/2026</t>
         </is>
       </c>
     </row>
@@ -38812,7 +38780,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 24/09/2026</t>
+          <t>Report as at 25/09/2026</t>
         </is>
       </c>
     </row>
@@ -43337,7 +43305,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 24/09/2026</t>
+          <t>Report as at 25/09/2026</t>
         </is>
       </c>
     </row>
@@ -45121,7 +45089,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 24/09/2026</t>
+          <t>Report as at 25/09/2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -542,7 +542,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 25/09/2026</t>
+          <t>Report as at 26/09/2026</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 25/09/2026</t>
+          <t>Report as at 26/09/2026</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 25/09/2026</t>
+          <t>Report as at 26/09/2026</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 25/09/2026</t>
+          <t>Report as at 26/09/2026</t>
         </is>
       </c>
     </row>
@@ -6991,7 +6991,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 25/09/2026</t>
+          <t>Report as at 26/09/2026</t>
         </is>
       </c>
     </row>
@@ -7768,7 +7768,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 25/09/2026</t>
+          <t>Report as at 26/09/2026</t>
         </is>
       </c>
     </row>
@@ -8335,7 +8335,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 25/09/2026</t>
+          <t>Report as at 26/09/2026</t>
         </is>
       </c>
     </row>
@@ -8859,7 +8859,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 25/09/2026</t>
+          <t>Report as at 26/09/2026</t>
         </is>
       </c>
     </row>
@@ -9687,7 +9687,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 25/09/2026</t>
+          <t>Report as at 26/09/2026</t>
         </is>
       </c>
     </row>
@@ -10498,7 +10498,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 25/09/2026</t>
+          <t>Report as at 26/09/2026</t>
         </is>
       </c>
     </row>
@@ -11077,7 +11077,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 25/09/2026</t>
+          <t>Report as at 26/09/2026</t>
         </is>
       </c>
     </row>
@@ -11600,7 +11600,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 25/09/2026</t>
+          <t>Report as at 26/09/2026</t>
         </is>
       </c>
     </row>
@@ -12322,7 +12322,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 25/09/2026</t>
+          <t>Report as at 26/09/2026</t>
         </is>
       </c>
     </row>
@@ -17794,7 +17794,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 25/09/2026</t>
+          <t>Report as at 26/09/2026</t>
         </is>
       </c>
     </row>
@@ -18851,7 +18851,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 25/09/2026</t>
+          <t>Report as at 26/09/2026</t>
         </is>
       </c>
     </row>
@@ -24842,7 +24842,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 25/09/2026</t>
+          <t>Report as at 26/09/2026</t>
         </is>
       </c>
     </row>
@@ -25645,7 +25645,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 25/09/2026</t>
+          <t>Report as at 26/09/2026</t>
         </is>
       </c>
     </row>
@@ -26197,7 +26197,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 25/09/2026</t>
+          <t>Report as at 26/09/2026</t>
         </is>
       </c>
     </row>
@@ -32903,7 +32903,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 25/09/2026</t>
+          <t>Report as at 26/09/2026</t>
         </is>
       </c>
     </row>
@@ -33480,7 +33480,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 25/09/2026</t>
+          <t>Report as at 26/09/2026</t>
         </is>
       </c>
     </row>
@@ -33986,7 +33986,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 25/09/2026</t>
+          <t>Report as at 26/09/2026</t>
         </is>
       </c>
     </row>
@@ -35473,7 +35473,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 25/09/2026</t>
+          <t>Report as at 26/09/2026</t>
         </is>
       </c>
     </row>
@@ -35779,7 +35779,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 25/09/2026</t>
+          <t>Report as at 26/09/2026</t>
         </is>
       </c>
     </row>
@@ -37186,7 +37186,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 25/09/2026</t>
+          <t>Report as at 26/09/2026</t>
         </is>
       </c>
     </row>
@@ -38046,7 +38046,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 25/09/2026</t>
+          <t>Report as at 26/09/2026</t>
         </is>
       </c>
     </row>
@@ -38780,7 +38780,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 25/09/2026</t>
+          <t>Report as at 26/09/2026</t>
         </is>
       </c>
     </row>
@@ -43305,7 +43305,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 25/09/2026</t>
+          <t>Report as at 26/09/2026</t>
         </is>
       </c>
     </row>
@@ -45089,7 +45089,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 25/09/2026</t>
+          <t>Report as at 26/09/2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -542,7 +542,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 26/09/2026</t>
+          <t>Report as at 27/09/2026</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 26/09/2026</t>
+          <t>Report as at 27/09/2026</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 26/09/2026</t>
+          <t>Report as at 27/09/2026</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 26/09/2026</t>
+          <t>Report as at 27/09/2026</t>
         </is>
       </c>
     </row>
@@ -6991,7 +6991,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 26/09/2026</t>
+          <t>Report as at 27/09/2026</t>
         </is>
       </c>
     </row>
@@ -7768,7 +7768,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 26/09/2026</t>
+          <t>Report as at 27/09/2026</t>
         </is>
       </c>
     </row>
@@ -8335,7 +8335,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 26/09/2026</t>
+          <t>Report as at 27/09/2026</t>
         </is>
       </c>
     </row>
@@ -8859,7 +8859,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 26/09/2026</t>
+          <t>Report as at 27/09/2026</t>
         </is>
       </c>
     </row>
@@ -9687,7 +9687,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 26/09/2026</t>
+          <t>Report as at 27/09/2026</t>
         </is>
       </c>
     </row>
@@ -10498,7 +10498,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 26/09/2026</t>
+          <t>Report as at 27/09/2026</t>
         </is>
       </c>
     </row>
@@ -11077,7 +11077,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 26/09/2026</t>
+          <t>Report as at 27/09/2026</t>
         </is>
       </c>
     </row>
@@ -11600,7 +11600,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 26/09/2026</t>
+          <t>Report as at 27/09/2026</t>
         </is>
       </c>
     </row>
@@ -12322,7 +12322,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 26/09/2026</t>
+          <t>Report as at 27/09/2026</t>
         </is>
       </c>
     </row>
@@ -17794,7 +17794,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 26/09/2026</t>
+          <t>Report as at 27/09/2026</t>
         </is>
       </c>
     </row>
@@ -18851,7 +18851,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 26/09/2026</t>
+          <t>Report as at 27/09/2026</t>
         </is>
       </c>
     </row>
@@ -24842,7 +24842,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 26/09/2026</t>
+          <t>Report as at 27/09/2026</t>
         </is>
       </c>
     </row>
@@ -25645,7 +25645,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 26/09/2026</t>
+          <t>Report as at 27/09/2026</t>
         </is>
       </c>
     </row>
@@ -26197,7 +26197,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 26/09/2026</t>
+          <t>Report as at 27/09/2026</t>
         </is>
       </c>
     </row>
@@ -32903,7 +32903,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 26/09/2026</t>
+          <t>Report as at 27/09/2026</t>
         </is>
       </c>
     </row>
@@ -33480,7 +33480,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 26/09/2026</t>
+          <t>Report as at 27/09/2026</t>
         </is>
       </c>
     </row>
@@ -33986,7 +33986,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 26/09/2026</t>
+          <t>Report as at 27/09/2026</t>
         </is>
       </c>
     </row>
@@ -35473,7 +35473,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 26/09/2026</t>
+          <t>Report as at 27/09/2026</t>
         </is>
       </c>
     </row>
@@ -35779,7 +35779,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 26/09/2026</t>
+          <t>Report as at 27/09/2026</t>
         </is>
       </c>
     </row>
@@ -37186,7 +37186,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 26/09/2026</t>
+          <t>Report as at 27/09/2026</t>
         </is>
       </c>
     </row>
@@ -38046,7 +38046,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 26/09/2026</t>
+          <t>Report as at 27/09/2026</t>
         </is>
       </c>
     </row>
@@ -38780,7 +38780,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 26/09/2026</t>
+          <t>Report as at 27/09/2026</t>
         </is>
       </c>
     </row>
@@ -43305,7 +43305,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 26/09/2026</t>
+          <t>Report as at 27/09/2026</t>
         </is>
       </c>
     </row>
@@ -45089,7 +45089,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 26/09/2026</t>
+          <t>Report as at 27/09/2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -542,7 +542,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 27/09/2026</t>
+          <t>Report as at 28/09/2026</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 27/09/2026</t>
+          <t>Report as at 28/09/2026</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 27/09/2026</t>
+          <t>Report as at 28/09/2026</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 27/09/2026</t>
+          <t>Report as at 28/09/2026</t>
         </is>
       </c>
     </row>
@@ -6991,7 +6991,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 27/09/2026</t>
+          <t>Report as at 28/09/2026</t>
         </is>
       </c>
     </row>
@@ -7768,7 +7768,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 27/09/2026</t>
+          <t>Report as at 28/09/2026</t>
         </is>
       </c>
     </row>
@@ -8335,7 +8335,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 27/09/2026</t>
+          <t>Report as at 28/09/2026</t>
         </is>
       </c>
     </row>
@@ -8859,7 +8859,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 27/09/2026</t>
+          <t>Report as at 28/09/2026</t>
         </is>
       </c>
     </row>
@@ -9687,7 +9687,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 27/09/2026</t>
+          <t>Report as at 28/09/2026</t>
         </is>
       </c>
     </row>
@@ -10498,7 +10498,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 27/09/2026</t>
+          <t>Report as at 28/09/2026</t>
         </is>
       </c>
     </row>
@@ -11077,7 +11077,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 27/09/2026</t>
+          <t>Report as at 28/09/2026</t>
         </is>
       </c>
     </row>
@@ -11600,7 +11600,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 27/09/2026</t>
+          <t>Report as at 28/09/2026</t>
         </is>
       </c>
     </row>
@@ -12322,7 +12322,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 27/09/2026</t>
+          <t>Report as at 28/09/2026</t>
         </is>
       </c>
     </row>
@@ -17794,7 +17794,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 27/09/2026</t>
+          <t>Report as at 28/09/2026</t>
         </is>
       </c>
     </row>
@@ -18851,7 +18851,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 27/09/2026</t>
+          <t>Report as at 28/09/2026</t>
         </is>
       </c>
     </row>
@@ -24842,7 +24842,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 27/09/2026</t>
+          <t>Report as at 28/09/2026</t>
         </is>
       </c>
     </row>
@@ -25645,7 +25645,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 27/09/2026</t>
+          <t>Report as at 28/09/2026</t>
         </is>
       </c>
     </row>
@@ -26197,7 +26197,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 27/09/2026</t>
+          <t>Report as at 28/09/2026</t>
         </is>
       </c>
     </row>
@@ -32903,7 +32903,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 27/09/2026</t>
+          <t>Report as at 28/09/2026</t>
         </is>
       </c>
     </row>
@@ -33480,7 +33480,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 27/09/2026</t>
+          <t>Report as at 28/09/2026</t>
         </is>
       </c>
     </row>
@@ -33986,7 +33986,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 27/09/2026</t>
+          <t>Report as at 28/09/2026</t>
         </is>
       </c>
     </row>
@@ -35473,7 +35473,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 27/09/2026</t>
+          <t>Report as at 28/09/2026</t>
         </is>
       </c>
     </row>
@@ -35779,7 +35779,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 27/09/2026</t>
+          <t>Report as at 28/09/2026</t>
         </is>
       </c>
     </row>
@@ -37186,7 +37186,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 27/09/2026</t>
+          <t>Report as at 28/09/2026</t>
         </is>
       </c>
     </row>
@@ -38046,7 +38046,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 27/09/2026</t>
+          <t>Report as at 28/09/2026</t>
         </is>
       </c>
     </row>
@@ -38780,7 +38780,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 27/09/2026</t>
+          <t>Report as at 28/09/2026</t>
         </is>
       </c>
     </row>
@@ -43305,7 +43305,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 27/09/2026</t>
+          <t>Report as at 28/09/2026</t>
         </is>
       </c>
     </row>
@@ -45089,7 +45089,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 27/09/2026</t>
+          <t>Report as at 28/09/2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -542,7 +542,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 28/09/2026</t>
+          <t>Report as at 29/09/2026</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 28/09/2026</t>
+          <t>Report as at 29/09/2026</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 28/09/2026</t>
+          <t>Report as at 29/09/2026</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 28/09/2026</t>
+          <t>Report as at 29/09/2026</t>
         </is>
       </c>
     </row>
@@ -6991,7 +6991,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 28/09/2026</t>
+          <t>Report as at 29/09/2026</t>
         </is>
       </c>
     </row>
@@ -7768,7 +7768,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 28/09/2026</t>
+          <t>Report as at 29/09/2026</t>
         </is>
       </c>
     </row>
@@ -8335,7 +8335,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 28/09/2026</t>
+          <t>Report as at 29/09/2026</t>
         </is>
       </c>
     </row>
@@ -8835,7 +8835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:P16"/>
+  <dimension ref="A2:P17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -8859,7 +8859,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 28/09/2026</t>
+          <t>Report as at 29/09/2026</t>
         </is>
       </c>
     </row>
@@ -9652,6 +9652,42 @@
         <v/>
       </c>
       <c r="P16" s="8" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>VISTA TIARA 1</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="n">
+        <v>46293</v>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>704</v>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>30688-2</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>MB WORLD PROPERTIES SDN. BHD.</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="n"/>
+      <c r="H17" s="10" t="n"/>
+      <c r="I17" s="11" t="n"/>
+      <c r="J17" s="10" t="n"/>
+      <c r="K17" s="10" t="n"/>
+      <c r="L17" s="11" t="n"/>
+      <c r="M17" s="12" t="n"/>
+      <c r="N17" s="12" t="n"/>
+      <c r="O17" s="13" t="n"/>
+      <c r="P17" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -9687,7 +9723,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 28/09/2026</t>
+          <t>Report as at 29/09/2026</t>
         </is>
       </c>
     </row>
@@ -10498,7 +10534,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 28/09/2026</t>
+          <t>Report as at 29/09/2026</t>
         </is>
       </c>
     </row>
@@ -11077,7 +11113,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 28/09/2026</t>
+          <t>Report as at 29/09/2026</t>
         </is>
       </c>
     </row>
@@ -11600,7 +11636,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 28/09/2026</t>
+          <t>Report as at 29/09/2026</t>
         </is>
       </c>
     </row>
@@ -12322,7 +12358,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 28/09/2026</t>
+          <t>Report as at 29/09/2026</t>
         </is>
       </c>
     </row>
@@ -17794,7 +17830,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 28/09/2026</t>
+          <t>Report as at 29/09/2026</t>
         </is>
       </c>
     </row>
@@ -18851,7 +18887,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 28/09/2026</t>
+          <t>Report as at 29/09/2026</t>
         </is>
       </c>
     </row>
@@ -24842,7 +24878,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 28/09/2026</t>
+          <t>Report as at 29/09/2026</t>
         </is>
       </c>
     </row>
@@ -25645,7 +25681,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 28/09/2026</t>
+          <t>Report as at 29/09/2026</t>
         </is>
       </c>
     </row>
@@ -26197,7 +26233,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 28/09/2026</t>
+          <t>Report as at 29/09/2026</t>
         </is>
       </c>
     </row>
@@ -32903,7 +32939,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 28/09/2026</t>
+          <t>Report as at 29/09/2026</t>
         </is>
       </c>
     </row>
@@ -33480,7 +33516,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 28/09/2026</t>
+          <t>Report as at 29/09/2026</t>
         </is>
       </c>
     </row>
@@ -33986,7 +34022,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 28/09/2026</t>
+          <t>Report as at 29/09/2026</t>
         </is>
       </c>
     </row>
@@ -35473,7 +35509,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 28/09/2026</t>
+          <t>Report as at 29/09/2026</t>
         </is>
       </c>
     </row>
@@ -35779,7 +35815,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 28/09/2026</t>
+          <t>Report as at 29/09/2026</t>
         </is>
       </c>
     </row>
@@ -37186,7 +37222,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 28/09/2026</t>
+          <t>Report as at 29/09/2026</t>
         </is>
       </c>
     </row>
@@ -38046,7 +38082,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 28/09/2026</t>
+          <t>Report as at 29/09/2026</t>
         </is>
       </c>
     </row>
@@ -38780,7 +38816,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 28/09/2026</t>
+          <t>Report as at 29/09/2026</t>
         </is>
       </c>
     </row>
@@ -43305,7 +43341,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 28/09/2026</t>
+          <t>Report as at 29/09/2026</t>
         </is>
       </c>
     </row>
@@ -45089,7 +45125,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 28/09/2026</t>
+          <t>Report as at 29/09/2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -542,7 +542,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 29/09/2026</t>
+          <t>Report as at 30/09/2026</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 29/09/2026</t>
+          <t>Report as at 30/09/2026</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 29/09/2026</t>
+          <t>Report as at 30/09/2026</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 29/09/2026</t>
+          <t>Report as at 30/09/2026</t>
         </is>
       </c>
     </row>
@@ -6991,7 +6991,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 29/09/2026</t>
+          <t>Report as at 30/09/2026</t>
         </is>
       </c>
     </row>
@@ -7768,7 +7768,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 29/09/2026</t>
+          <t>Report as at 30/09/2026</t>
         </is>
       </c>
     </row>
@@ -8335,7 +8335,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 29/09/2026</t>
+          <t>Report as at 30/09/2026</t>
         </is>
       </c>
     </row>
@@ -8859,7 +8859,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 29/09/2026</t>
+          <t>Report as at 30/09/2026</t>
         </is>
       </c>
     </row>
@@ -9723,7 +9723,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 29/09/2026</t>
+          <t>Report as at 30/09/2026</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 29/09/2026</t>
+          <t>Report as at 30/09/2026</t>
         </is>
       </c>
     </row>
@@ -11113,7 +11113,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 29/09/2026</t>
+          <t>Report as at 30/09/2026</t>
         </is>
       </c>
     </row>
@@ -11636,7 +11636,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 29/09/2026</t>
+          <t>Report as at 30/09/2026</t>
         </is>
       </c>
     </row>
@@ -12358,7 +12358,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 29/09/2026</t>
+          <t>Report as at 30/09/2026</t>
         </is>
       </c>
     </row>
@@ -17830,7 +17830,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 29/09/2026</t>
+          <t>Report as at 30/09/2026</t>
         </is>
       </c>
     </row>
@@ -18887,7 +18887,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 29/09/2026</t>
+          <t>Report as at 30/09/2026</t>
         </is>
       </c>
     </row>
@@ -24878,7 +24878,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 29/09/2026</t>
+          <t>Report as at 30/09/2026</t>
         </is>
       </c>
     </row>
@@ -25681,7 +25681,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 29/09/2026</t>
+          <t>Report as at 30/09/2026</t>
         </is>
       </c>
     </row>
@@ -26233,7 +26233,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 29/09/2026</t>
+          <t>Report as at 30/09/2026</t>
         </is>
       </c>
     </row>
@@ -32939,7 +32939,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 29/09/2026</t>
+          <t>Report as at 30/09/2026</t>
         </is>
       </c>
     </row>
@@ -33516,7 +33516,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 29/09/2026</t>
+          <t>Report as at 30/09/2026</t>
         </is>
       </c>
     </row>
@@ -34022,7 +34022,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 29/09/2026</t>
+          <t>Report as at 30/09/2026</t>
         </is>
       </c>
     </row>
@@ -35509,7 +35509,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 29/09/2026</t>
+          <t>Report as at 30/09/2026</t>
         </is>
       </c>
     </row>
@@ -35815,7 +35815,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 29/09/2026</t>
+          <t>Report as at 30/09/2026</t>
         </is>
       </c>
     </row>
@@ -37222,7 +37222,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 29/09/2026</t>
+          <t>Report as at 30/09/2026</t>
         </is>
       </c>
     </row>
@@ -38082,7 +38082,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 29/09/2026</t>
+          <t>Report as at 30/09/2026</t>
         </is>
       </c>
     </row>
@@ -38816,7 +38816,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 29/09/2026</t>
+          <t>Report as at 30/09/2026</t>
         </is>
       </c>
     </row>
@@ -43341,7 +43341,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 29/09/2026</t>
+          <t>Report as at 30/09/2026</t>
         </is>
       </c>
     </row>
@@ -45125,7 +45125,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 29/09/2026</t>
+          <t>Report as at 30/09/2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -542,7 +542,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 30/09/2026</t>
+          <t>Report as at 01/10/2026</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 30/09/2026</t>
+          <t>Report as at 01/10/2026</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 30/09/2026</t>
+          <t>Report as at 01/10/2026</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 30/09/2026</t>
+          <t>Report as at 01/10/2026</t>
         </is>
       </c>
     </row>
@@ -6991,7 +6991,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 30/09/2026</t>
+          <t>Report as at 01/10/2026</t>
         </is>
       </c>
     </row>
@@ -7768,7 +7768,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 30/09/2026</t>
+          <t>Report as at 01/10/2026</t>
         </is>
       </c>
     </row>
@@ -8335,7 +8335,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 30/09/2026</t>
+          <t>Report as at 01/10/2026</t>
         </is>
       </c>
     </row>
@@ -8859,7 +8859,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 30/09/2026</t>
+          <t>Report as at 01/10/2026</t>
         </is>
       </c>
     </row>
@@ -9723,7 +9723,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 30/09/2026</t>
+          <t>Report as at 01/10/2026</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 30/09/2026</t>
+          <t>Report as at 01/10/2026</t>
         </is>
       </c>
     </row>
@@ -11113,7 +11113,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 30/09/2026</t>
+          <t>Report as at 01/10/2026</t>
         </is>
       </c>
     </row>
@@ -11636,7 +11636,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 30/09/2026</t>
+          <t>Report as at 01/10/2026</t>
         </is>
       </c>
     </row>
@@ -12358,7 +12358,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 30/09/2026</t>
+          <t>Report as at 01/10/2026</t>
         </is>
       </c>
     </row>
@@ -17830,7 +17830,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 30/09/2026</t>
+          <t>Report as at 01/10/2026</t>
         </is>
       </c>
     </row>
@@ -18887,7 +18887,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 30/09/2026</t>
+          <t>Report as at 01/10/2026</t>
         </is>
       </c>
     </row>
@@ -24878,7 +24878,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 30/09/2026</t>
+          <t>Report as at 01/10/2026</t>
         </is>
       </c>
     </row>
@@ -25681,7 +25681,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 30/09/2026</t>
+          <t>Report as at 01/10/2026</t>
         </is>
       </c>
     </row>
@@ -26233,7 +26233,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 30/09/2026</t>
+          <t>Report as at 01/10/2026</t>
         </is>
       </c>
     </row>
@@ -32939,7 +32939,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 30/09/2026</t>
+          <t>Report as at 01/10/2026</t>
         </is>
       </c>
     </row>
@@ -33516,7 +33516,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 30/09/2026</t>
+          <t>Report as at 01/10/2026</t>
         </is>
       </c>
     </row>
@@ -34022,7 +34022,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 30/09/2026</t>
+          <t>Report as at 01/10/2026</t>
         </is>
       </c>
     </row>
@@ -35509,7 +35509,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 30/09/2026</t>
+          <t>Report as at 01/10/2026</t>
         </is>
       </c>
     </row>
@@ -35815,7 +35815,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 30/09/2026</t>
+          <t>Report as at 01/10/2026</t>
         </is>
       </c>
     </row>
@@ -37222,7 +37222,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 30/09/2026</t>
+          <t>Report as at 01/10/2026</t>
         </is>
       </c>
     </row>
@@ -38082,7 +38082,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 30/09/2026</t>
+          <t>Report as at 01/10/2026</t>
         </is>
       </c>
     </row>
@@ -38816,7 +38816,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 30/09/2026</t>
+          <t>Report as at 01/10/2026</t>
         </is>
       </c>
     </row>
@@ -43341,7 +43341,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 30/09/2026</t>
+          <t>Report as at 01/10/2026</t>
         </is>
       </c>
     </row>
@@ -45125,7 +45125,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 30/09/2026</t>
+          <t>Report as at 01/10/2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 01/10/2026</t>
+          <t>Report as at 02/10/2026</t>
         </is>
       </c>
     </row>
@@ -1952,7 +1952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:S40"/>
+  <dimension ref="A2:S41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1979,7 +1979,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 01/10/2026</t>
+          <t>Report as at 02/10/2026</t>
         </is>
       </c>
     </row>
@@ -4521,6 +4521,50 @@
         <v/>
       </c>
       <c r="S40" s="8" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>LA' AVIERA@SERENA</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="n">
+        <v>46296</v>
+      </c>
+      <c r="D41" s="10" t="n">
+        <v>1056</v>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>11225-15</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>BLOSSOM EASTLAND SDN. BHD.</t>
+        </is>
+      </c>
+      <c r="G41" s="10" t="n"/>
+      <c r="H41" s="10" t="n"/>
+      <c r="I41" s="11" t="n"/>
+      <c r="J41" s="10" t="n"/>
+      <c r="K41" s="10" t="n"/>
+      <c r="L41" s="11" t="n"/>
+      <c r="M41" s="10" t="n"/>
+      <c r="N41" s="10" t="n"/>
+      <c r="O41" s="11" t="n"/>
+      <c r="P41" s="12" t="n"/>
+      <c r="Q41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" s="13">
+        <f>Q41/$D$41</f>
+        <v/>
+      </c>
+      <c r="S41" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -4566,7 +4610,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 01/10/2026</t>
+          <t>Report as at 02/10/2026</t>
         </is>
       </c>
     </row>
@@ -6494,7 +6538,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 01/10/2026</t>
+          <t>Report as at 02/10/2026</t>
         </is>
       </c>
     </row>
@@ -8133,7 +8177,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 01/10/2026</t>
+          <t>Report as at 02/10/2026</t>
         </is>
       </c>
     </row>
@@ -9026,7 +9070,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 01/10/2026</t>
+          <t>Report as at 02/10/2026</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9725,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 01/10/2026</t>
+          <t>Report as at 02/10/2026</t>
         </is>
       </c>
     </row>
@@ -10282,7 +10326,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 01/10/2026</t>
+          <t>Report as at 02/10/2026</t>
         </is>
       </c>
     </row>
@@ -11279,7 +11323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:M23"/>
+  <dimension ref="A2:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -11300,7 +11344,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 01/10/2026</t>
+          <t>Report as at 02/10/2026</t>
         </is>
       </c>
     </row>
@@ -12296,6 +12340,44 @@
         <v/>
       </c>
       <c r="M23" s="8" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>TAMAN BELIMBING</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>46296</v>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>7935-10</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>SMART BUDGET ECONOMY SDN. BHD.</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="n"/>
+      <c r="H24" s="10" t="n"/>
+      <c r="I24" s="11" t="n"/>
+      <c r="J24" s="12" t="n"/>
+      <c r="K24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="13">
+        <f>K24/$D$24</f>
+        <v/>
+      </c>
+      <c r="M24" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -12342,7 +12424,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 01/10/2026</t>
+          <t>Report as at 02/10/2026</t>
         </is>
       </c>
     </row>
@@ -13009,7 +13091,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 01/10/2026</t>
+          <t>Report as at 02/10/2026</t>
         </is>
       </c>
     </row>
@@ -13609,7 +13691,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 01/10/2026</t>
+          <t>Report as at 02/10/2026</t>
         </is>
       </c>
     </row>
@@ -14409,7 +14491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:S97"/>
+  <dimension ref="A2:S98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -14436,7 +14518,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 01/10/2026</t>
+          <t>Report as at 02/10/2026</t>
         </is>
       </c>
     </row>
@@ -20908,6 +20990,50 @@
         <v/>
       </c>
       <c r="S97" s="8" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="7" t="n">
+        <v>94</v>
+      </c>
+      <c r="B98" s="8" t="inlineStr">
+        <is>
+          <t>BANDAR SCIENTEX JASIN PRESINT 3</t>
+        </is>
+      </c>
+      <c r="C98" s="9" t="n">
+        <v>46296</v>
+      </c>
+      <c r="D98" s="10" t="n">
+        <v>252</v>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>6575-60</t>
+        </is>
+      </c>
+      <c r="F98" s="8" t="inlineStr">
+        <is>
+          <t>SCIENTEX HEIGHTS SDN. BHD.</t>
+        </is>
+      </c>
+      <c r="G98" s="10" t="n"/>
+      <c r="H98" s="10" t="n"/>
+      <c r="I98" s="11" t="n"/>
+      <c r="J98" s="10" t="n"/>
+      <c r="K98" s="10" t="n"/>
+      <c r="L98" s="11" t="n"/>
+      <c r="M98" s="10" t="n"/>
+      <c r="N98" s="10" t="n"/>
+      <c r="O98" s="11" t="n"/>
+      <c r="P98" s="12" t="n"/>
+      <c r="Q98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" s="13">
+        <f>Q98/$D$98</f>
+        <v/>
+      </c>
+      <c r="S98" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -20953,7 +21079,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 01/10/2026</t>
+          <t>Report as at 02/10/2026</t>
         </is>
       </c>
     </row>
@@ -22208,7 +22334,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 01/10/2026</t>
+          <t>Report as at 02/10/2026</t>
         </is>
       </c>
     </row>
@@ -29368,7 +29494,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 01/10/2026</t>
+          <t>Report as at 02/10/2026</t>
         </is>
       </c>
     </row>
@@ -30314,7 +30440,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 01/10/2026</t>
+          <t>Report as at 02/10/2026</t>
         </is>
       </c>
     </row>
@@ -30954,7 +31080,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 01/10/2026</t>
+          <t>Report as at 02/10/2026</t>
         </is>
       </c>
     </row>
@@ -38980,7 +39106,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 01/10/2026</t>
+          <t>Report as at 02/10/2026</t>
         </is>
       </c>
     </row>
@@ -39630,7 +39756,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 01/10/2026</t>
+          <t>Report as at 02/10/2026</t>
         </is>
       </c>
     </row>
@@ -40208,7 +40334,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 01/10/2026</t>
+          <t>Report as at 02/10/2026</t>
         </is>
       </c>
     </row>
@@ -41970,7 +42096,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 01/10/2026</t>
+          <t>Report as at 02/10/2026</t>
         </is>
       </c>
     </row>
@@ -42315,7 +42441,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 01/10/2026</t>
+          <t>Report as at 02/10/2026</t>
         </is>
       </c>
     </row>
@@ -43978,7 +44104,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 01/10/2026</t>
+          <t>Report as at 02/10/2026</t>
         </is>
       </c>
     </row>
@@ -44970,7 +45096,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 01/10/2026</t>
+          <t>Report as at 02/10/2026</t>
         </is>
       </c>
     </row>
@@ -45831,7 +45957,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 01/10/2026</t>
+          <t>Report as at 02/10/2026</t>
         </is>
       </c>
     </row>
@@ -51225,7 +51351,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 01/10/2026</t>
+          <t>Report as at 02/10/2026</t>
         </is>
       </c>
     </row>
@@ -53295,7 +53421,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 01/10/2026</t>
+          <t>Report as at 02/10/2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 02/10/2026</t>
+          <t>Report as at 03/10/2026</t>
         </is>
       </c>
     </row>
@@ -1979,7 +1979,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 02/10/2026</t>
+          <t>Report as at 03/10/2026</t>
         </is>
       </c>
     </row>
@@ -4610,7 +4610,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 02/10/2026</t>
+          <t>Report as at 03/10/2026</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 02/10/2026</t>
+          <t>Report as at 03/10/2026</t>
         </is>
       </c>
     </row>
@@ -8177,7 +8177,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 02/10/2026</t>
+          <t>Report as at 03/10/2026</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9070,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 02/10/2026</t>
+          <t>Report as at 03/10/2026</t>
         </is>
       </c>
     </row>
@@ -9725,7 +9725,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 02/10/2026</t>
+          <t>Report as at 03/10/2026</t>
         </is>
       </c>
     </row>
@@ -10326,7 +10326,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 02/10/2026</t>
+          <t>Report as at 03/10/2026</t>
         </is>
       </c>
     </row>
@@ -11344,7 +11344,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 02/10/2026</t>
+          <t>Report as at 03/10/2026</t>
         </is>
       </c>
     </row>
@@ -12424,7 +12424,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 02/10/2026</t>
+          <t>Report as at 03/10/2026</t>
         </is>
       </c>
     </row>
@@ -13091,7 +13091,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 02/10/2026</t>
+          <t>Report as at 03/10/2026</t>
         </is>
       </c>
     </row>
@@ -13691,7 +13691,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 02/10/2026</t>
+          <t>Report as at 03/10/2026</t>
         </is>
       </c>
     </row>
@@ -14518,7 +14518,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 02/10/2026</t>
+          <t>Report as at 03/10/2026</t>
         </is>
       </c>
     </row>
@@ -21079,7 +21079,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 02/10/2026</t>
+          <t>Report as at 03/10/2026</t>
         </is>
       </c>
     </row>
@@ -22334,7 +22334,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 02/10/2026</t>
+          <t>Report as at 03/10/2026</t>
         </is>
       </c>
     </row>
@@ -29494,7 +29494,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 02/10/2026</t>
+          <t>Report as at 03/10/2026</t>
         </is>
       </c>
     </row>
@@ -30440,7 +30440,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 02/10/2026</t>
+          <t>Report as at 03/10/2026</t>
         </is>
       </c>
     </row>
@@ -31080,7 +31080,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 02/10/2026</t>
+          <t>Report as at 03/10/2026</t>
         </is>
       </c>
     </row>
@@ -39106,7 +39106,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 02/10/2026</t>
+          <t>Report as at 03/10/2026</t>
         </is>
       </c>
     </row>
@@ -39756,7 +39756,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 02/10/2026</t>
+          <t>Report as at 03/10/2026</t>
         </is>
       </c>
     </row>
@@ -40334,7 +40334,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 02/10/2026</t>
+          <t>Report as at 03/10/2026</t>
         </is>
       </c>
     </row>
@@ -42096,7 +42096,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 02/10/2026</t>
+          <t>Report as at 03/10/2026</t>
         </is>
       </c>
     </row>
@@ -42441,7 +42441,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 02/10/2026</t>
+          <t>Report as at 03/10/2026</t>
         </is>
       </c>
     </row>
@@ -44104,7 +44104,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 02/10/2026</t>
+          <t>Report as at 03/10/2026</t>
         </is>
       </c>
     </row>
@@ -45096,7 +45096,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 02/10/2026</t>
+          <t>Report as at 03/10/2026</t>
         </is>
       </c>
     </row>
@@ -45957,7 +45957,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 02/10/2026</t>
+          <t>Report as at 03/10/2026</t>
         </is>
       </c>
     </row>
@@ -51351,7 +51351,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 02/10/2026</t>
+          <t>Report as at 03/10/2026</t>
         </is>
       </c>
     </row>
@@ -53421,7 +53421,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 02/10/2026</t>
+          <t>Report as at 03/10/2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 03/10/2026</t>
+          <t>Report as at 04/10/2026</t>
         </is>
       </c>
     </row>
@@ -1979,7 +1979,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 03/10/2026</t>
+          <t>Report as at 04/10/2026</t>
         </is>
       </c>
     </row>
@@ -4610,7 +4610,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 03/10/2026</t>
+          <t>Report as at 04/10/2026</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 03/10/2026</t>
+          <t>Report as at 04/10/2026</t>
         </is>
       </c>
     </row>
@@ -8177,7 +8177,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 03/10/2026</t>
+          <t>Report as at 04/10/2026</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9070,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 03/10/2026</t>
+          <t>Report as at 04/10/2026</t>
         </is>
       </c>
     </row>
@@ -9725,7 +9725,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 03/10/2026</t>
+          <t>Report as at 04/10/2026</t>
         </is>
       </c>
     </row>
@@ -10326,7 +10326,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 03/10/2026</t>
+          <t>Report as at 04/10/2026</t>
         </is>
       </c>
     </row>
@@ -11344,7 +11344,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 03/10/2026</t>
+          <t>Report as at 04/10/2026</t>
         </is>
       </c>
     </row>
@@ -12424,7 +12424,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 03/10/2026</t>
+          <t>Report as at 04/10/2026</t>
         </is>
       </c>
     </row>
@@ -13091,7 +13091,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 03/10/2026</t>
+          <t>Report as at 04/10/2026</t>
         </is>
       </c>
     </row>
@@ -13691,7 +13691,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 03/10/2026</t>
+          <t>Report as at 04/10/2026</t>
         </is>
       </c>
     </row>
@@ -14518,7 +14518,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 03/10/2026</t>
+          <t>Report as at 04/10/2026</t>
         </is>
       </c>
     </row>
@@ -21079,7 +21079,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 03/10/2026</t>
+          <t>Report as at 04/10/2026</t>
         </is>
       </c>
     </row>
@@ -22334,7 +22334,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 03/10/2026</t>
+          <t>Report as at 04/10/2026</t>
         </is>
       </c>
     </row>
@@ -29494,7 +29494,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 03/10/2026</t>
+          <t>Report as at 04/10/2026</t>
         </is>
       </c>
     </row>
@@ -30440,7 +30440,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 03/10/2026</t>
+          <t>Report as at 04/10/2026</t>
         </is>
       </c>
     </row>
@@ -31080,7 +31080,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 03/10/2026</t>
+          <t>Report as at 04/10/2026</t>
         </is>
       </c>
     </row>
@@ -39106,7 +39106,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 03/10/2026</t>
+          <t>Report as at 04/10/2026</t>
         </is>
       </c>
     </row>
@@ -39756,7 +39756,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 03/10/2026</t>
+          <t>Report as at 04/10/2026</t>
         </is>
       </c>
     </row>
@@ -40334,7 +40334,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 03/10/2026</t>
+          <t>Report as at 04/10/2026</t>
         </is>
       </c>
     </row>
@@ -42096,7 +42096,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 03/10/2026</t>
+          <t>Report as at 04/10/2026</t>
         </is>
       </c>
     </row>
@@ -42441,7 +42441,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 03/10/2026</t>
+          <t>Report as at 04/10/2026</t>
         </is>
       </c>
     </row>
@@ -44104,7 +44104,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 03/10/2026</t>
+          <t>Report as at 04/10/2026</t>
         </is>
       </c>
     </row>
@@ -45096,7 +45096,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 03/10/2026</t>
+          <t>Report as at 04/10/2026</t>
         </is>
       </c>
     </row>
@@ -45957,7 +45957,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 03/10/2026</t>
+          <t>Report as at 04/10/2026</t>
         </is>
       </c>
     </row>
@@ -51351,7 +51351,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 03/10/2026</t>
+          <t>Report as at 04/10/2026</t>
         </is>
       </c>
     </row>
@@ -53421,7 +53421,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 03/10/2026</t>
+          <t>Report as at 04/10/2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 04/10/2026</t>
+          <t>Report as at 05/10/2026</t>
         </is>
       </c>
     </row>
@@ -1979,7 +1979,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 04/10/2026</t>
+          <t>Report as at 05/10/2026</t>
         </is>
       </c>
     </row>
@@ -4610,7 +4610,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 04/10/2026</t>
+          <t>Report as at 05/10/2026</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 04/10/2026</t>
+          <t>Report as at 05/10/2026</t>
         </is>
       </c>
     </row>
@@ -8177,7 +8177,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 04/10/2026</t>
+          <t>Report as at 05/10/2026</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9070,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 04/10/2026</t>
+          <t>Report as at 05/10/2026</t>
         </is>
       </c>
     </row>
@@ -9725,7 +9725,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 04/10/2026</t>
+          <t>Report as at 05/10/2026</t>
         </is>
       </c>
     </row>
@@ -10326,7 +10326,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 04/10/2026</t>
+          <t>Report as at 05/10/2026</t>
         </is>
       </c>
     </row>
@@ -11344,7 +11344,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 04/10/2026</t>
+          <t>Report as at 05/10/2026</t>
         </is>
       </c>
     </row>
@@ -12424,7 +12424,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 04/10/2026</t>
+          <t>Report as at 05/10/2026</t>
         </is>
       </c>
     </row>
@@ -13091,7 +13091,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 04/10/2026</t>
+          <t>Report as at 05/10/2026</t>
         </is>
       </c>
     </row>
@@ -13691,7 +13691,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 04/10/2026</t>
+          <t>Report as at 05/10/2026</t>
         </is>
       </c>
     </row>
@@ -14518,7 +14518,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 04/10/2026</t>
+          <t>Report as at 05/10/2026</t>
         </is>
       </c>
     </row>
@@ -21079,7 +21079,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 04/10/2026</t>
+          <t>Report as at 05/10/2026</t>
         </is>
       </c>
     </row>
@@ -22334,7 +22334,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 04/10/2026</t>
+          <t>Report as at 05/10/2026</t>
         </is>
       </c>
     </row>
@@ -29494,7 +29494,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 04/10/2026</t>
+          <t>Report as at 05/10/2026</t>
         </is>
       </c>
     </row>
@@ -30440,7 +30440,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 04/10/2026</t>
+          <t>Report as at 05/10/2026</t>
         </is>
       </c>
     </row>
@@ -31080,7 +31080,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 04/10/2026</t>
+          <t>Report as at 05/10/2026</t>
         </is>
       </c>
     </row>
@@ -39106,7 +39106,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 04/10/2026</t>
+          <t>Report as at 05/10/2026</t>
         </is>
       </c>
     </row>
@@ -39756,7 +39756,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 04/10/2026</t>
+          <t>Report as at 05/10/2026</t>
         </is>
       </c>
     </row>
@@ -40334,7 +40334,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 04/10/2026</t>
+          <t>Report as at 05/10/2026</t>
         </is>
       </c>
     </row>
@@ -42096,7 +42096,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 04/10/2026</t>
+          <t>Report as at 05/10/2026</t>
         </is>
       </c>
     </row>
@@ -42441,7 +42441,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 04/10/2026</t>
+          <t>Report as at 05/10/2026</t>
         </is>
       </c>
     </row>
@@ -44104,7 +44104,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 04/10/2026</t>
+          <t>Report as at 05/10/2026</t>
         </is>
       </c>
     </row>
@@ -45096,7 +45096,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 04/10/2026</t>
+          <t>Report as at 05/10/2026</t>
         </is>
       </c>
     </row>
@@ -45957,7 +45957,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 04/10/2026</t>
+          <t>Report as at 05/10/2026</t>
         </is>
       </c>
     </row>
@@ -51351,7 +51351,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 04/10/2026</t>
+          <t>Report as at 05/10/2026</t>
         </is>
       </c>
     </row>
@@ -53421,7 +53421,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 04/10/2026</t>
+          <t>Report as at 05/10/2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 05/10/2026</t>
+          <t>Report as at 06/10/2026</t>
         </is>
       </c>
     </row>
@@ -1979,7 +1979,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 05/10/2026</t>
+          <t>Report as at 06/10/2026</t>
         </is>
       </c>
     </row>
@@ -4610,7 +4610,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 05/10/2026</t>
+          <t>Report as at 06/10/2026</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 05/10/2026</t>
+          <t>Report as at 06/10/2026</t>
         </is>
       </c>
     </row>
@@ -8177,7 +8177,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 05/10/2026</t>
+          <t>Report as at 06/10/2026</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9070,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 05/10/2026</t>
+          <t>Report as at 06/10/2026</t>
         </is>
       </c>
     </row>
@@ -9725,7 +9725,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 05/10/2026</t>
+          <t>Report as at 06/10/2026</t>
         </is>
       </c>
     </row>
@@ -10326,7 +10326,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 05/10/2026</t>
+          <t>Report as at 06/10/2026</t>
         </is>
       </c>
     </row>
@@ -11344,7 +11344,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 05/10/2026</t>
+          <t>Report as at 06/10/2026</t>
         </is>
       </c>
     </row>
@@ -12424,7 +12424,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 05/10/2026</t>
+          <t>Report as at 06/10/2026</t>
         </is>
       </c>
     </row>
@@ -13091,7 +13091,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 05/10/2026</t>
+          <t>Report as at 06/10/2026</t>
         </is>
       </c>
     </row>
@@ -13691,7 +13691,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 05/10/2026</t>
+          <t>Report as at 06/10/2026</t>
         </is>
       </c>
     </row>
@@ -14518,7 +14518,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 05/10/2026</t>
+          <t>Report as at 06/10/2026</t>
         </is>
       </c>
     </row>
@@ -21079,7 +21079,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 05/10/2026</t>
+          <t>Report as at 06/10/2026</t>
         </is>
       </c>
     </row>
@@ -22334,7 +22334,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 05/10/2026</t>
+          <t>Report as at 06/10/2026</t>
         </is>
       </c>
     </row>
@@ -29494,7 +29494,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 05/10/2026</t>
+          <t>Report as at 06/10/2026</t>
         </is>
       </c>
     </row>
@@ -30440,7 +30440,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 05/10/2026</t>
+          <t>Report as at 06/10/2026</t>
         </is>
       </c>
     </row>
@@ -31080,7 +31080,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 05/10/2026</t>
+          <t>Report as at 06/10/2026</t>
         </is>
       </c>
     </row>
@@ -39106,7 +39106,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 05/10/2026</t>
+          <t>Report as at 06/10/2026</t>
         </is>
       </c>
     </row>
@@ -39756,7 +39756,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 05/10/2026</t>
+          <t>Report as at 06/10/2026</t>
         </is>
       </c>
     </row>
@@ -40334,7 +40334,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 05/10/2026</t>
+          <t>Report as at 06/10/2026</t>
         </is>
       </c>
     </row>
@@ -42096,7 +42096,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 05/10/2026</t>
+          <t>Report as at 06/10/2026</t>
         </is>
       </c>
     </row>
@@ -42441,7 +42441,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 05/10/2026</t>
+          <t>Report as at 06/10/2026</t>
         </is>
       </c>
     </row>
@@ -44104,7 +44104,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 05/10/2026</t>
+          <t>Report as at 06/10/2026</t>
         </is>
       </c>
     </row>
@@ -45096,7 +45096,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 05/10/2026</t>
+          <t>Report as at 06/10/2026</t>
         </is>
       </c>
     </row>
@@ -45957,7 +45957,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 05/10/2026</t>
+          <t>Report as at 06/10/2026</t>
         </is>
       </c>
     </row>
@@ -51351,7 +51351,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 05/10/2026</t>
+          <t>Report as at 06/10/2026</t>
         </is>
       </c>
     </row>
@@ -53421,7 +53421,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 05/10/2026</t>
+          <t>Report as at 06/10/2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 06/10/2026</t>
+          <t>Report as at 07/10/2026</t>
         </is>
       </c>
     </row>
@@ -1979,7 +1979,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 06/10/2026</t>
+          <t>Report as at 07/10/2026</t>
         </is>
       </c>
     </row>
@@ -4610,7 +4610,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 06/10/2026</t>
+          <t>Report as at 07/10/2026</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 06/10/2026</t>
+          <t>Report as at 07/10/2026</t>
         </is>
       </c>
     </row>
@@ -8177,7 +8177,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 06/10/2026</t>
+          <t>Report as at 07/10/2026</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9070,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 06/10/2026</t>
+          <t>Report as at 07/10/2026</t>
         </is>
       </c>
     </row>
@@ -9725,7 +9725,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 06/10/2026</t>
+          <t>Report as at 07/10/2026</t>
         </is>
       </c>
     </row>
@@ -10326,7 +10326,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 06/10/2026</t>
+          <t>Report as at 07/10/2026</t>
         </is>
       </c>
     </row>
@@ -11344,7 +11344,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 06/10/2026</t>
+          <t>Report as at 07/10/2026</t>
         </is>
       </c>
     </row>
@@ -12424,7 +12424,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 06/10/2026</t>
+          <t>Report as at 07/10/2026</t>
         </is>
       </c>
     </row>
@@ -13091,7 +13091,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 06/10/2026</t>
+          <t>Report as at 07/10/2026</t>
         </is>
       </c>
     </row>
@@ -13691,7 +13691,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 06/10/2026</t>
+          <t>Report as at 07/10/2026</t>
         </is>
       </c>
     </row>
@@ -14518,7 +14518,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 06/10/2026</t>
+          <t>Report as at 07/10/2026</t>
         </is>
       </c>
     </row>
@@ -21079,7 +21079,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 06/10/2026</t>
+          <t>Report as at 07/10/2026</t>
         </is>
       </c>
     </row>
@@ -22334,7 +22334,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 06/10/2026</t>
+          <t>Report as at 07/10/2026</t>
         </is>
       </c>
     </row>
@@ -29494,7 +29494,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 06/10/2026</t>
+          <t>Report as at 07/10/2026</t>
         </is>
       </c>
     </row>
@@ -30440,7 +30440,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 06/10/2026</t>
+          <t>Report as at 07/10/2026</t>
         </is>
       </c>
     </row>
@@ -31080,7 +31080,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 06/10/2026</t>
+          <t>Report as at 07/10/2026</t>
         </is>
       </c>
     </row>
@@ -39106,7 +39106,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 06/10/2026</t>
+          <t>Report as at 07/10/2026</t>
         </is>
       </c>
     </row>
@@ -39756,7 +39756,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 06/10/2026</t>
+          <t>Report as at 07/10/2026</t>
         </is>
       </c>
     </row>
@@ -40334,7 +40334,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 06/10/2026</t>
+          <t>Report as at 07/10/2026</t>
         </is>
       </c>
     </row>
@@ -42096,7 +42096,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 06/10/2026</t>
+          <t>Report as at 07/10/2026</t>
         </is>
       </c>
     </row>
@@ -42441,7 +42441,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 06/10/2026</t>
+          <t>Report as at 07/10/2026</t>
         </is>
       </c>
     </row>
@@ -44104,7 +44104,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 06/10/2026</t>
+          <t>Report as at 07/10/2026</t>
         </is>
       </c>
     </row>
@@ -45096,7 +45096,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 06/10/2026</t>
+          <t>Report as at 07/10/2026</t>
         </is>
       </c>
     </row>
@@ -45957,7 +45957,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 06/10/2026</t>
+          <t>Report as at 07/10/2026</t>
         </is>
       </c>
     </row>
@@ -51351,7 +51351,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 06/10/2026</t>
+          <t>Report as at 07/10/2026</t>
         </is>
       </c>
     </row>
@@ -53421,7 +53421,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 06/10/2026</t>
+          <t>Report as at 07/10/2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 07/10/2026</t>
+          <t>Report as at 08/10/2026</t>
         </is>
       </c>
     </row>
@@ -1979,7 +1979,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 07/10/2026</t>
+          <t>Report as at 08/10/2026</t>
         </is>
       </c>
     </row>
@@ -4610,7 +4610,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 07/10/2026</t>
+          <t>Report as at 08/10/2026</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 07/10/2026</t>
+          <t>Report as at 08/10/2026</t>
         </is>
       </c>
     </row>
@@ -8177,7 +8177,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 07/10/2026</t>
+          <t>Report as at 08/10/2026</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9070,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 07/10/2026</t>
+          <t>Report as at 08/10/2026</t>
         </is>
       </c>
     </row>
@@ -9725,7 +9725,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 07/10/2026</t>
+          <t>Report as at 08/10/2026</t>
         </is>
       </c>
     </row>
@@ -10326,7 +10326,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 07/10/2026</t>
+          <t>Report as at 08/10/2026</t>
         </is>
       </c>
     </row>
@@ -11344,7 +11344,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 07/10/2026</t>
+          <t>Report as at 08/10/2026</t>
         </is>
       </c>
     </row>
@@ -12424,7 +12424,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 07/10/2026</t>
+          <t>Report as at 08/10/2026</t>
         </is>
       </c>
     </row>
@@ -13091,7 +13091,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 07/10/2026</t>
+          <t>Report as at 08/10/2026</t>
         </is>
       </c>
     </row>
@@ -13691,7 +13691,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 07/10/2026</t>
+          <t>Report as at 08/10/2026</t>
         </is>
       </c>
     </row>
@@ -14518,7 +14518,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 07/10/2026</t>
+          <t>Report as at 08/10/2026</t>
         </is>
       </c>
     </row>
@@ -21079,7 +21079,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 07/10/2026</t>
+          <t>Report as at 08/10/2026</t>
         </is>
       </c>
     </row>
@@ -22334,7 +22334,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 07/10/2026</t>
+          <t>Report as at 08/10/2026</t>
         </is>
       </c>
     </row>
@@ -29494,7 +29494,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 07/10/2026</t>
+          <t>Report as at 08/10/2026</t>
         </is>
       </c>
     </row>
@@ -30440,7 +30440,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 07/10/2026</t>
+          <t>Report as at 08/10/2026</t>
         </is>
       </c>
     </row>
@@ -31080,7 +31080,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 07/10/2026</t>
+          <t>Report as at 08/10/2026</t>
         </is>
       </c>
     </row>
@@ -39106,7 +39106,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 07/10/2026</t>
+          <t>Report as at 08/10/2026</t>
         </is>
       </c>
     </row>
@@ -39756,7 +39756,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 07/10/2026</t>
+          <t>Report as at 08/10/2026</t>
         </is>
       </c>
     </row>
@@ -40334,7 +40334,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 07/10/2026</t>
+          <t>Report as at 08/10/2026</t>
         </is>
       </c>
     </row>
@@ -42096,7 +42096,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 07/10/2026</t>
+          <t>Report as at 08/10/2026</t>
         </is>
       </c>
     </row>
@@ -42441,7 +42441,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 07/10/2026</t>
+          <t>Report as at 08/10/2026</t>
         </is>
       </c>
     </row>
@@ -44104,7 +44104,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 07/10/2026</t>
+          <t>Report as at 08/10/2026</t>
         </is>
       </c>
     </row>
@@ -45096,7 +45096,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 07/10/2026</t>
+          <t>Report as at 08/10/2026</t>
         </is>
       </c>
     </row>
@@ -45957,7 +45957,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 07/10/2026</t>
+          <t>Report as at 08/10/2026</t>
         </is>
       </c>
     </row>
@@ -51351,7 +51351,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 07/10/2026</t>
+          <t>Report as at 08/10/2026</t>
         </is>
       </c>
     </row>
@@ -53421,7 +53421,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 07/10/2026</t>
+          <t>Report as at 08/10/2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -548,7 +548,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 08/10/2026</t>
+          <t>Report as at 09/10/2026</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2180,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 08/10/2026</t>
+          <t>Report as at 09/10/2026</t>
         </is>
       </c>
     </row>
@@ -5240,7 +5240,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 08/10/2026</t>
+          <t>Report as at 09/10/2026</t>
         </is>
       </c>
     </row>
@@ -7471,7 +7471,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 08/10/2026</t>
+          <t>Report as at 09/10/2026</t>
         </is>
       </c>
     </row>
@@ -9330,7 +9330,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 08/10/2026</t>
+          <t>Report as at 09/10/2026</t>
         </is>
       </c>
     </row>
@@ -10339,7 +10339,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 08/10/2026</t>
+          <t>Report as at 09/10/2026</t>
         </is>
       </c>
     </row>
@@ -11082,7 +11082,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 08/10/2026</t>
+          <t>Report as at 09/10/2026</t>
         </is>
       </c>
     </row>
@@ -11760,7 +11760,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 08/10/2026</t>
+          <t>Report as at 09/10/2026</t>
         </is>
       </c>
     </row>
@@ -12939,7 +12939,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 08/10/2026</t>
+          <t>Report as at 09/10/2026</t>
         </is>
       </c>
     </row>
@@ -14261,7 +14261,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 08/10/2026</t>
+          <t>Report as at 09/10/2026</t>
         </is>
       </c>
     </row>
@@ -15016,7 +15016,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 08/10/2026</t>
+          <t>Report as at 09/10/2026</t>
         </is>
       </c>
     </row>
@@ -15693,7 +15693,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 08/10/2026</t>
+          <t>Report as at 09/10/2026</t>
         </is>
       </c>
     </row>
@@ -16595,7 +16595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:V98"/>
+  <dimension ref="A2:V99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -16625,7 +16625,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 08/10/2026</t>
+          <t>Report as at 09/10/2026</t>
         </is>
       </c>
     </row>
@@ -24193,6 +24193,53 @@
         <v/>
       </c>
       <c r="V98" s="8" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="7" t="n">
+        <v>95</v>
+      </c>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>TAMAN SCIENTEX SUNGAI DUA</t>
+        </is>
+      </c>
+      <c r="C99" s="9" t="n">
+        <v>46303</v>
+      </c>
+      <c r="D99" s="10" t="n">
+        <v>200</v>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>9294-90</t>
+        </is>
+      </c>
+      <c r="F99" s="8" t="inlineStr">
+        <is>
+          <t>SCIENTEX QUATARI SDN. BHD.</t>
+        </is>
+      </c>
+      <c r="G99" s="10" t="n"/>
+      <c r="H99" s="10" t="n"/>
+      <c r="I99" s="11" t="n"/>
+      <c r="J99" s="10" t="n"/>
+      <c r="K99" s="10" t="n"/>
+      <c r="L99" s="11" t="n"/>
+      <c r="M99" s="10" t="n"/>
+      <c r="N99" s="10" t="n"/>
+      <c r="O99" s="11" t="n"/>
+      <c r="P99" s="10" t="n"/>
+      <c r="Q99" s="10" t="n"/>
+      <c r="R99" s="11" t="n"/>
+      <c r="S99" s="12" t="n"/>
+      <c r="T99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U99" s="13">
+        <f>T99/$D$99</f>
+        <v/>
+      </c>
+      <c r="V99" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -24242,7 +24289,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 08/10/2026</t>
+          <t>Report as at 09/10/2026</t>
         </is>
       </c>
     </row>
@@ -25695,7 +25742,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 08/10/2026</t>
+          <t>Report as at 09/10/2026</t>
         </is>
       </c>
     </row>
@@ -34024,7 +34071,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 08/10/2026</t>
+          <t>Report as at 09/10/2026</t>
         </is>
       </c>
     </row>
@@ -35113,7 +35160,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 08/10/2026</t>
+          <t>Report as at 09/10/2026</t>
         </is>
       </c>
     </row>
@@ -35841,7 +35888,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 08/10/2026</t>
+          <t>Report as at 09/10/2026</t>
         </is>
       </c>
     </row>
@@ -45187,7 +45234,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 08/10/2026</t>
+          <t>Report as at 09/10/2026</t>
         </is>
       </c>
     </row>
@@ -45910,7 +45957,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 08/10/2026</t>
+          <t>Report as at 09/10/2026</t>
         </is>
       </c>
     </row>
@@ -46560,7 +46607,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 08/10/2026</t>
+          <t>Report as at 09/10/2026</t>
         </is>
       </c>
     </row>
@@ -48597,7 +48644,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 08/10/2026</t>
+          <t>Report as at 09/10/2026</t>
         </is>
       </c>
     </row>
@@ -48981,7 +49028,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 08/10/2026</t>
+          <t>Report as at 09/10/2026</t>
         </is>
       </c>
     </row>
@@ -50900,7 +50947,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 08/10/2026</t>
+          <t>Report as at 09/10/2026</t>
         </is>
       </c>
     </row>
@@ -52024,7 +52071,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 08/10/2026</t>
+          <t>Report as at 09/10/2026</t>
         </is>
       </c>
     </row>
@@ -53012,7 +53059,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 08/10/2026</t>
+          <t>Report as at 09/10/2026</t>
         </is>
       </c>
     </row>
@@ -59275,7 +59322,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 08/10/2026</t>
+          <t>Report as at 09/10/2026</t>
         </is>
       </c>
     </row>
@@ -61601,7 +61648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:V49"/>
+  <dimension ref="A2:V50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -61631,7 +61678,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 08/10/2026</t>
+          <t>Report as at 09/10/2026</t>
         </is>
       </c>
     </row>
@@ -65257,6 +65304,53 @@
       </c>
       <c r="V49" s="8" t="inlineStr"/>
     </row>
+    <row r="50">
+      <c r="A50" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>RESIDENSI LESTARI TEBRAU</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="n">
+        <v>46303</v>
+      </c>
+      <c r="D50" s="10" t="n">
+        <v>1228</v>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>3390-87</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>KHOO SOON LEE REALTY SDN. BHD.</t>
+        </is>
+      </c>
+      <c r="G50" s="10" t="n"/>
+      <c r="H50" s="10" t="n"/>
+      <c r="I50" s="11" t="n"/>
+      <c r="J50" s="10" t="n"/>
+      <c r="K50" s="10" t="n"/>
+      <c r="L50" s="11" t="n"/>
+      <c r="M50" s="10" t="n"/>
+      <c r="N50" s="10" t="n"/>
+      <c r="O50" s="11" t="n"/>
+      <c r="P50" s="10" t="n"/>
+      <c r="Q50" s="10" t="n"/>
+      <c r="R50" s="11" t="n"/>
+      <c r="S50" s="12" t="n"/>
+      <c r="T50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" s="13">
+        <f>T50/$D$50</f>
+        <v/>
+      </c>
+      <c r="V50" s="8" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="M3:O3"/>

--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -548,7 +548,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 09/10/2026</t>
+          <t>Report as at 10/10/2026</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2180,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 09/10/2026</t>
+          <t>Report as at 10/10/2026</t>
         </is>
       </c>
     </row>
@@ -5240,7 +5240,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 09/10/2026</t>
+          <t>Report as at 10/10/2026</t>
         </is>
       </c>
     </row>
@@ -7471,7 +7471,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 09/10/2026</t>
+          <t>Report as at 10/10/2026</t>
         </is>
       </c>
     </row>
@@ -9330,7 +9330,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 09/10/2026</t>
+          <t>Report as at 10/10/2026</t>
         </is>
       </c>
     </row>
@@ -10339,7 +10339,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 09/10/2026</t>
+          <t>Report as at 10/10/2026</t>
         </is>
       </c>
     </row>
@@ -11082,7 +11082,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 09/10/2026</t>
+          <t>Report as at 10/10/2026</t>
         </is>
       </c>
     </row>
@@ -11760,7 +11760,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 09/10/2026</t>
+          <t>Report as at 10/10/2026</t>
         </is>
       </c>
     </row>
@@ -12939,7 +12939,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 09/10/2026</t>
+          <t>Report as at 10/10/2026</t>
         </is>
       </c>
     </row>
@@ -14261,7 +14261,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 09/10/2026</t>
+          <t>Report as at 10/10/2026</t>
         </is>
       </c>
     </row>
@@ -15016,7 +15016,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 09/10/2026</t>
+          <t>Report as at 10/10/2026</t>
         </is>
       </c>
     </row>
@@ -15693,7 +15693,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 09/10/2026</t>
+          <t>Report as at 10/10/2026</t>
         </is>
       </c>
     </row>
@@ -16625,7 +16625,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 09/10/2026</t>
+          <t>Report as at 10/10/2026</t>
         </is>
       </c>
     </row>
@@ -24289,7 +24289,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 09/10/2026</t>
+          <t>Report as at 10/10/2026</t>
         </is>
       </c>
     </row>
@@ -25742,7 +25742,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 09/10/2026</t>
+          <t>Report as at 10/10/2026</t>
         </is>
       </c>
     </row>
@@ -34071,7 +34071,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 09/10/2026</t>
+          <t>Report as at 10/10/2026</t>
         </is>
       </c>
     </row>
@@ -35160,7 +35160,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 09/10/2026</t>
+          <t>Report as at 10/10/2026</t>
         </is>
       </c>
     </row>
@@ -35888,7 +35888,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 09/10/2026</t>
+          <t>Report as at 10/10/2026</t>
         </is>
       </c>
     </row>
@@ -45234,7 +45234,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 09/10/2026</t>
+          <t>Report as at 10/10/2026</t>
         </is>
       </c>
     </row>
@@ -45957,7 +45957,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 09/10/2026</t>
+          <t>Report as at 10/10/2026</t>
         </is>
       </c>
     </row>
@@ -46607,7 +46607,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 09/10/2026</t>
+          <t>Report as at 10/10/2026</t>
         </is>
       </c>
     </row>
@@ -48644,7 +48644,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 09/10/2026</t>
+          <t>Report as at 10/10/2026</t>
         </is>
       </c>
     </row>
@@ -49028,7 +49028,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 09/10/2026</t>
+          <t>Report as at 10/10/2026</t>
         </is>
       </c>
     </row>
@@ -50947,7 +50947,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 09/10/2026</t>
+          <t>Report as at 10/10/2026</t>
         </is>
       </c>
     </row>
@@ -52071,7 +52071,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 09/10/2026</t>
+          <t>Report as at 10/10/2026</t>
         </is>
       </c>
     </row>
@@ -53059,7 +53059,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 09/10/2026</t>
+          <t>Report as at 10/10/2026</t>
         </is>
       </c>
     </row>
@@ -59322,7 +59322,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 09/10/2026</t>
+          <t>Report as at 10/10/2026</t>
         </is>
       </c>
     </row>
@@ -61678,7 +61678,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 09/10/2026</t>
+          <t>Report as at 10/10/2026</t>
         </is>
       </c>
     </row>
